--- a/Diagramma di Gantt.xlsx
+++ b/Diagramma di Gantt.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948CD877-4746-4539-B5E8-3417178A8906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45A4D9E-2BA8-4A79-B3AF-5DFA82A43CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1168,6 +1168,9 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="27" fillId="10" borderId="2" xfId="10" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
@@ -1186,64 +1189,61 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="10" borderId="2" xfId="10" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="54">
-    <cellStyle name="20% - Colore 1" xfId="31" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Colore 2" xfId="35" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Colore 3" xfId="39" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Colore 4" xfId="43" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Colore 5" xfId="47" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Colore 6" xfId="51" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Colore 1" xfId="32" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Colore 2" xfId="36" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Colore 3" xfId="40" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Colore 4" xfId="44" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Colore 5" xfId="48" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Colore 6" xfId="52" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Colore 1" xfId="33" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Colore 2" xfId="37" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Colore 3" xfId="41" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Colore 4" xfId="45" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Colore 5" xfId="49" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Colore 6" xfId="53" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="31" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="35" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="39" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="43" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="47" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="51" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="32" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="36" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="40" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="44" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="48" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="52" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="33" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="37" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="41" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="45" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="49" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="53" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="30" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="34" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="38" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="42" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="46" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="50" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Attività" xfId="12" xr:uid="{6391D789-272B-4DD2-9BF3-2CDCF610FA41}"/>
-    <cellStyle name="Calcolo" xfId="23" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Cella collegata" xfId="24" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Cella da controllare" xfId="25" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8" customBuiltin="1"/>
-    <cellStyle name="Collegamento ipertestuale visitato" xfId="13" builtinId="9" customBuiltin="1"/>
-    <cellStyle name="Colore 1" xfId="30" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Colore 2" xfId="34" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Colore 3" xfId="38" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Colore 4" xfId="42" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Colore 5" xfId="46" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Colore 6" xfId="50" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="23" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="25" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
+    <cellStyle name="Comma [0]" xfId="14" builtinId="6" customBuiltin="1"/>
+    <cellStyle name="Currency" xfId="15" builtinId="4" customBuiltin="1"/>
+    <cellStyle name="Currency [0]" xfId="16" builtinId="7" customBuiltin="1"/>
     <cellStyle name="Data" xfId="10" xr:uid="{229918B6-DD13-4F5A-97B9-305F7E002AA3}"/>
+    <cellStyle name="Explanatory Text" xfId="28" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="13" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="18" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="6" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="7" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="8" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="17" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Inizio progetto" xfId="9" xr:uid="{8EB8A09A-C31C-40A3-B2C1-9449520178B8}"/>
     <cellStyle name="Input" xfId="21" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Migliaia" xfId="4" builtinId="3" customBuiltin="1"/>
-    <cellStyle name="Migliaia [0]" xfId="14" builtinId="6" customBuiltin="1"/>
-    <cellStyle name="Neutrale" xfId="20" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="24" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="20" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Nome" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Nota" xfId="27" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="27" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="22" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Percentuale" xfId="2" builtinId="5" customBuiltin="1"/>
-    <cellStyle name="Testo avviso" xfId="26" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Testo descrittivo" xfId="28" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Titolo" xfId="5" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Titolo 1" xfId="6" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Titolo 2" xfId="7" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Titolo 3" xfId="8" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Titolo 4" xfId="17" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Totale" xfId="29" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Valore non valido" xfId="19" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Valore valido" xfId="18" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Valuta" xfId="15" builtinId="4" customBuiltin="1"/>
-    <cellStyle name="Valuta [0]" xfId="16" builtinId="7" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="29" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="26" builtinId="11" customBuiltin="1"/>
     <cellStyle name="zTestoNascosto" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
   <dxfs count="14">
@@ -1807,97 +1807,97 @@
       <c r="B3" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="74"/>
-      <c r="E3" s="78">
+      <c r="D3" s="75"/>
+      <c r="E3" s="79">
         <f ca="1">TODAY()</f>
-        <v>45649</v>
-      </c>
-      <c r="F3" s="78"/>
+        <v>45650</v>
+      </c>
+      <c r="F3" s="79"/>
     </row>
     <row r="4" spans="1:56" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="74"/>
+      <c r="D4" s="75"/>
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="H4" s="75">
+      <c r="H4" s="76">
         <f ca="1">H5</f>
         <v>45649</v>
       </c>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="75">
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="76">
         <f ca="1">O5</f>
         <v>45656</v>
       </c>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="75">
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="76">
         <f ca="1">V5</f>
         <v>45663</v>
       </c>
-      <c r="W4" s="76"/>
-      <c r="X4" s="76"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
-      <c r="AB4" s="77"/>
-      <c r="AC4" s="75">
+      <c r="W4" s="77"/>
+      <c r="X4" s="77"/>
+      <c r="Y4" s="77"/>
+      <c r="Z4" s="77"/>
+      <c r="AA4" s="77"/>
+      <c r="AB4" s="78"/>
+      <c r="AC4" s="76">
         <f ca="1">AC5</f>
         <v>45670</v>
       </c>
-      <c r="AD4" s="76"/>
-      <c r="AE4" s="76"/>
-      <c r="AF4" s="76"/>
-      <c r="AG4" s="76"/>
-      <c r="AH4" s="76"/>
-      <c r="AI4" s="77"/>
-      <c r="AJ4" s="75">
+      <c r="AD4" s="77"/>
+      <c r="AE4" s="77"/>
+      <c r="AF4" s="77"/>
+      <c r="AG4" s="77"/>
+      <c r="AH4" s="77"/>
+      <c r="AI4" s="78"/>
+      <c r="AJ4" s="76">
         <f ca="1">AJ5</f>
         <v>45677</v>
       </c>
-      <c r="AK4" s="76"/>
-      <c r="AL4" s="76"/>
-      <c r="AM4" s="76"/>
-      <c r="AN4" s="76"/>
-      <c r="AO4" s="76"/>
-      <c r="AP4" s="77"/>
-      <c r="AQ4" s="75">
+      <c r="AK4" s="77"/>
+      <c r="AL4" s="77"/>
+      <c r="AM4" s="77"/>
+      <c r="AN4" s="77"/>
+      <c r="AO4" s="77"/>
+      <c r="AP4" s="78"/>
+      <c r="AQ4" s="76">
         <f ca="1">AQ5</f>
         <v>45684</v>
       </c>
-      <c r="AR4" s="76"/>
-      <c r="AS4" s="76"/>
-      <c r="AT4" s="76"/>
-      <c r="AU4" s="76"/>
-      <c r="AV4" s="76"/>
-      <c r="AW4" s="77"/>
-      <c r="AX4" s="75">
+      <c r="AR4" s="77"/>
+      <c r="AS4" s="77"/>
+      <c r="AT4" s="77"/>
+      <c r="AU4" s="77"/>
+      <c r="AV4" s="77"/>
+      <c r="AW4" s="78"/>
+      <c r="AX4" s="76">
         <f ca="1">AX5</f>
         <v>45691</v>
       </c>
-      <c r="AY4" s="76"/>
-      <c r="AZ4" s="76"/>
-      <c r="BA4" s="76"/>
-      <c r="BB4" s="76"/>
-      <c r="BC4" s="76"/>
-      <c r="BD4" s="77"/>
+      <c r="AY4" s="77"/>
+      <c r="AZ4" s="77"/>
+      <c r="BA4" s="77"/>
+      <c r="BB4" s="77"/>
+      <c r="BC4" s="77"/>
+      <c r="BD4" s="78"/>
     </row>
     <row r="5" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
@@ -2458,15 +2458,15 @@
         <v>43</v>
       </c>
       <c r="D9" s="13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E9" s="48">
         <f ca="1">Inizio_progetto</f>
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="F9" s="48">
         <f ca="1">E9</f>
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="G9" s="10">
         <f t="shared" ref="G9:G26" ca="1" si="5">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
@@ -2531,15 +2531,15 @@
         <v>35</v>
       </c>
       <c r="D10" s="13">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E10" s="48">
         <f ca="1">F9</f>
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="F10" s="48">
         <f ca="1">E10</f>
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="G10" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -2667,15 +2667,15 @@
         <v>36</v>
       </c>
       <c r="D12" s="16">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E12" s="51">
         <f ca="1">F10</f>
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="F12" s="51">
         <f ca="1">E12</f>
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="G12" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -2740,15 +2740,15 @@
         <v>43</v>
       </c>
       <c r="D13" s="16">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="51">
         <f ca="1">E12+1</f>
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="F13" s="51">
         <f t="shared" ref="F13:F15" ca="1" si="6">E13</f>
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="G13" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -2813,15 +2813,15 @@
         <v>43</v>
       </c>
       <c r="D14" s="16">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E14" s="51">
         <f ca="1">E13</f>
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="F14" s="51">
         <f t="shared" ca="1" si="6"/>
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="G14" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -2890,11 +2890,11 @@
       </c>
       <c r="E15" s="51">
         <f t="shared" ref="E15" ca="1" si="7">E14</f>
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="F15" s="51">
         <f t="shared" ca="1" si="6"/>
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="G15" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -2963,11 +2963,11 @@
       </c>
       <c r="E16" s="51">
         <f ca="1">F15+2</f>
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="F16" s="51">
         <f ca="1">E16</f>
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="G16" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3036,11 +3036,11 @@
       </c>
       <c r="E17" s="51">
         <f ca="1">E16</f>
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="F17" s="51">
         <f ca="1">E17</f>
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="G17" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3109,11 +3109,11 @@
       </c>
       <c r="E18" s="51">
         <f ca="1">E17</f>
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="F18" s="51">
         <f ca="1">E18</f>
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="G18" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3182,11 +3182,11 @@
       </c>
       <c r="E19" s="51">
         <f ca="1">E13</f>
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="F19" s="51">
         <f ca="1">E19+2</f>
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="G19" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3255,11 +3255,11 @@
       </c>
       <c r="E20" s="51">
         <f ca="1">F19+1</f>
-        <v>45653</v>
+        <v>45654</v>
       </c>
       <c r="F20" s="51">
         <f ca="1">E20+1</f>
-        <v>45654</v>
+        <v>45655</v>
       </c>
       <c r="G20" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3391,11 +3391,11 @@
       </c>
       <c r="E22" s="54">
         <f ca="1">F20+1</f>
-        <v>45655</v>
+        <v>45656</v>
       </c>
       <c r="F22" s="54">
         <f ca="1">E22+7</f>
-        <v>45662</v>
+        <v>45663</v>
       </c>
       <c r="G22" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3464,11 +3464,11 @@
       </c>
       <c r="E23" s="54">
         <f ca="1">E22</f>
-        <v>45655</v>
+        <v>45656</v>
       </c>
       <c r="F23" s="54">
         <f ca="1">E23+7</f>
-        <v>45662</v>
+        <v>45663</v>
       </c>
       <c r="G23" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3537,11 +3537,11 @@
       </c>
       <c r="E24" s="54">
         <f ca="1">E23</f>
-        <v>45655</v>
+        <v>45656</v>
       </c>
       <c r="F24" s="54">
         <f ca="1">E24+3</f>
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="G24" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3610,11 +3610,11 @@
       </c>
       <c r="E25" s="54">
         <f ca="1">F22+1</f>
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="F25" s="54">
         <f ca="1">E25+4</f>
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="G25" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3683,11 +3683,11 @@
       </c>
       <c r="E26" s="54">
         <f ca="1">F25-1</f>
-        <v>45666</v>
-      </c>
-      <c r="F26" s="79">
+        <v>45667</v>
+      </c>
+      <c r="F26" s="73">
         <f ca="1">E26+2</f>
-        <v>45668</v>
+        <v>45669</v>
       </c>
       <c r="G26" s="10">
         <f t="shared" ca="1" si="5"/>
@@ -3819,11 +3819,11 @@
       </c>
       <c r="E28" s="57">
         <f ca="1">F25+1</f>
-        <v>45668</v>
+        <v>45669</v>
       </c>
       <c r="F28" s="57">
         <f ca="1">E28+3</f>
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="G28" s="10">
         <f t="shared" ca="1" si="8"/>
@@ -3957,11 +3957,11 @@
       </c>
       <c r="E30" s="54">
         <f ca="1">F28</f>
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="F30" s="54">
         <f ca="1">E30+5</f>
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="G30" s="10">
         <f t="shared" ca="1" si="8"/>
@@ -4030,11 +4030,11 @@
       </c>
       <c r="E31" s="54">
         <f ca="1">E30</f>
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="F31" s="54">
         <f ca="1">E31+5</f>
-        <v>45676</v>
+        <v>45677</v>
       </c>
       <c r="G31" s="10">
         <f t="shared" ca="1" si="8"/>
@@ -4103,11 +4103,11 @@
       </c>
       <c r="E32" s="54">
         <f ca="1">E31</f>
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="F32" s="54">
         <f ca="1">E32+3</f>
-        <v>45674</v>
+        <v>45675</v>
       </c>
       <c r="G32" s="10">
         <f t="shared" ca="1" si="8"/>
@@ -4176,11 +4176,11 @@
       </c>
       <c r="E33" s="54">
         <f ca="1">F30+1</f>
-        <v>45677</v>
+        <v>45678</v>
       </c>
       <c r="F33" s="54">
         <f ca="1">E33+2</f>
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="G33" s="10">
         <f t="shared" ca="1" si="8"/>
@@ -4249,11 +4249,11 @@
       </c>
       <c r="E34" s="54">
         <f ca="1">F33-1</f>
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="F34" s="54">
         <f ca="1">E34+1</f>
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="G34" s="10">
         <f t="shared" ca="1" si="8"/>
@@ -4382,11 +4382,11 @@
       </c>
       <c r="E36" s="57">
         <f ca="1">F34+1</f>
-        <v>45680</v>
+        <v>45681</v>
       </c>
       <c r="F36" s="57">
         <f ca="1">E36+3</f>
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="G36" s="10">
         <f ca="1">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
@@ -4455,11 +4455,11 @@
       </c>
       <c r="E37" s="57">
         <f ca="1">F36</f>
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="F37" s="57">
         <f ca="1">F36</f>
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="G37" s="10">
         <f ca="1">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
@@ -4625,6 +4625,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003574973502B84C42B74035BA8AADE1A3" ma:contentTypeVersion="9" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ba771f4a91505810405fb99ac35d176">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8f4f0557-6568-4af7-94c6-f11cb446b9b2" xmlns:ns4="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3481e8909782aae8d117dfcc8e1ba87" ns3:_="" ns4:_="">
     <xsd:import namespace="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
@@ -4819,24 +4836,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A7A2A5-3EAC-4111-8CE5-4F4CD491981F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4853,29 +4878,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Diagramma di Gantt.xlsx
+++ b/Diagramma di Gantt.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45A4D9E-2BA8-4A79-B3AF-5DFA82A43CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B98E4B0-6ECD-4569-A369-5CAE2C233606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PianificazioneProgetto" sheetId="11" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
   <si>
     <t>Come creare la pianificazione di un progetto in questo foglio di lavoro.
 Immettere il titolo del progetto nella cella B1. 
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>Da bancherz</t>
+  </si>
+  <si>
+    <t>Tentori, Ronchi, Messa, Teruzzi</t>
   </si>
 </sst>
 </file>
@@ -223,7 +226,7 @@
     <numFmt numFmtId="168" formatCode="d\ mmm\ yyyy"/>
     <numFmt numFmtId="169" formatCode="d"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,14 +417,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -964,7 +959,7 @@
     <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1140,12 +1135,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="44" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1168,8 +1157,8 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="10" borderId="2" xfId="10" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="46" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
@@ -1191,59 +1180,59 @@
     </xf>
   </cellXfs>
   <cellStyles count="54">
-    <cellStyle name="20% - Accent1" xfId="31" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="35" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="39" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="43" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="47" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="51" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="32" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="36" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="40" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="44" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="48" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="52" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="33" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="37" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="41" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="45" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="49" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="53" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="30" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="34" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="38" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="42" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="46" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="50" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 1" xfId="31" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 2" xfId="35" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 3" xfId="39" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 4" xfId="43" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 5" xfId="47" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Colore 6" xfId="51" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 1" xfId="32" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 2" xfId="36" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 3" xfId="40" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 4" xfId="44" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 5" xfId="48" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Colore 6" xfId="52" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 1" xfId="33" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 2" xfId="37" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 3" xfId="41" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 4" xfId="45" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 5" xfId="49" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Colore 6" xfId="53" builtinId="52" customBuiltin="1"/>
     <cellStyle name="Attività" xfId="12" xr:uid="{6391D789-272B-4DD2-9BF3-2CDCF610FA41}"/>
-    <cellStyle name="Bad" xfId="19" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="23" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="25" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
-    <cellStyle name="Comma [0]" xfId="14" builtinId="6" customBuiltin="1"/>
-    <cellStyle name="Currency" xfId="15" builtinId="4" customBuiltin="1"/>
-    <cellStyle name="Currency [0]" xfId="16" builtinId="7" customBuiltin="1"/>
+    <cellStyle name="Calcolo" xfId="23" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Cella collegata" xfId="24" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Cella da controllare" xfId="25" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="Collegamento ipertestuale visitato" xfId="13" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="Colore 1" xfId="30" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Colore 2" xfId="34" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Colore 3" xfId="38" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Colore 4" xfId="42" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Colore 5" xfId="46" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Colore 6" xfId="50" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Data" xfId="10" xr:uid="{229918B6-DD13-4F5A-97B9-305F7E002AA3}"/>
-    <cellStyle name="Explanatory Text" xfId="28" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="13" builtinId="9" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="18" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="6" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="7" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="8" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="17" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Inizio progetto" xfId="9" xr:uid="{8EB8A09A-C31C-40A3-B2C1-9449520178B8}"/>
     <cellStyle name="Input" xfId="21" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="24" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="20" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Migliaia" xfId="4" builtinId="3" customBuiltin="1"/>
+    <cellStyle name="Migliaia [0]" xfId="14" builtinId="6" customBuiltin="1"/>
+    <cellStyle name="Neutrale" xfId="20" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Nome" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Note" xfId="27" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Nota" xfId="27" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="22" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="29" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="26" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Percentuale" xfId="2" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Testo avviso" xfId="26" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Testo descrittivo" xfId="28" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Titolo" xfId="5" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Titolo 1" xfId="6" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Titolo 2" xfId="7" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Titolo 3" xfId="8" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Titolo 4" xfId="17" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Totale" xfId="29" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Valore non valido" xfId="19" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Valore valido" xfId="18" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Valuta" xfId="15" builtinId="4" customBuiltin="1"/>
+    <cellStyle name="Valuta [0]" xfId="16" builtinId="7" customBuiltin="1"/>
     <cellStyle name="zTestoNascosto" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
   <dxfs count="14">
@@ -1807,97 +1796,96 @@
       <c r="B3" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="75"/>
-      <c r="E3" s="79">
-        <f ca="1">TODAY()</f>
-        <v>45650</v>
-      </c>
-      <c r="F3" s="79"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="77">
+        <v>45648</v>
+      </c>
+      <c r="F3" s="77"/>
     </row>
     <row r="4" spans="1:56" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="75"/>
+      <c r="D4" s="73"/>
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="H4" s="76">
-        <f ca="1">H5</f>
+      <c r="H4" s="74">
+        <f>H5</f>
         <v>45649</v>
       </c>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="78"/>
-      <c r="O4" s="76">
-        <f ca="1">O5</f>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="74">
+        <f>O5</f>
         <v>45656</v>
       </c>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="78"/>
-      <c r="V4" s="76">
-        <f ca="1">V5</f>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="76"/>
+      <c r="V4" s="74">
+        <f>V5</f>
         <v>45663</v>
       </c>
-      <c r="W4" s="77"/>
-      <c r="X4" s="77"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
-      <c r="AA4" s="77"/>
-      <c r="AB4" s="78"/>
-      <c r="AC4" s="76">
-        <f ca="1">AC5</f>
+      <c r="W4" s="75"/>
+      <c r="X4" s="75"/>
+      <c r="Y4" s="75"/>
+      <c r="Z4" s="75"/>
+      <c r="AA4" s="75"/>
+      <c r="AB4" s="76"/>
+      <c r="AC4" s="74">
+        <f>AC5</f>
         <v>45670</v>
       </c>
-      <c r="AD4" s="77"/>
-      <c r="AE4" s="77"/>
-      <c r="AF4" s="77"/>
-      <c r="AG4" s="77"/>
-      <c r="AH4" s="77"/>
-      <c r="AI4" s="78"/>
-      <c r="AJ4" s="76">
-        <f ca="1">AJ5</f>
+      <c r="AD4" s="75"/>
+      <c r="AE4" s="75"/>
+      <c r="AF4" s="75"/>
+      <c r="AG4" s="75"/>
+      <c r="AH4" s="75"/>
+      <c r="AI4" s="76"/>
+      <c r="AJ4" s="74">
+        <f>AJ5</f>
         <v>45677</v>
       </c>
-      <c r="AK4" s="77"/>
-      <c r="AL4" s="77"/>
-      <c r="AM4" s="77"/>
-      <c r="AN4" s="77"/>
-      <c r="AO4" s="77"/>
-      <c r="AP4" s="78"/>
-      <c r="AQ4" s="76">
-        <f ca="1">AQ5</f>
+      <c r="AK4" s="75"/>
+      <c r="AL4" s="75"/>
+      <c r="AM4" s="75"/>
+      <c r="AN4" s="75"/>
+      <c r="AO4" s="75"/>
+      <c r="AP4" s="76"/>
+      <c r="AQ4" s="74">
+        <f>AQ5</f>
         <v>45684</v>
       </c>
-      <c r="AR4" s="77"/>
-      <c r="AS4" s="77"/>
-      <c r="AT4" s="77"/>
-      <c r="AU4" s="77"/>
-      <c r="AV4" s="77"/>
-      <c r="AW4" s="78"/>
-      <c r="AX4" s="76">
-        <f ca="1">AX5</f>
+      <c r="AR4" s="75"/>
+      <c r="AS4" s="75"/>
+      <c r="AT4" s="75"/>
+      <c r="AU4" s="75"/>
+      <c r="AV4" s="75"/>
+      <c r="AW4" s="76"/>
+      <c r="AX4" s="74">
+        <f>AX5</f>
         <v>45691</v>
       </c>
-      <c r="AY4" s="77"/>
-      <c r="AZ4" s="77"/>
-      <c r="BA4" s="77"/>
-      <c r="BB4" s="77"/>
-      <c r="BC4" s="77"/>
-      <c r="BD4" s="78"/>
+      <c r="AY4" s="75"/>
+      <c r="AZ4" s="75"/>
+      <c r="BA4" s="75"/>
+      <c r="BB4" s="75"/>
+      <c r="BC4" s="75"/>
+      <c r="BD4" s="76"/>
     </row>
     <row r="5" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
@@ -1909,204 +1897,204 @@
       <c r="E5" s="43"/>
       <c r="F5" s="43"/>
       <c r="H5" s="58">
-        <f ca="1">Inizio_progetto-WEEKDAY(Inizio_progetto,1)+2+7*(Visualizza_settimana-1)</f>
+        <f>Inizio_progetto-WEEKDAY(Inizio_progetto,1)+2+7*(Visualizza_settimana-1)</f>
         <v>45649</v>
       </c>
       <c r="I5" s="59">
-        <f ca="1">H5+1</f>
+        <f>H5+1</f>
         <v>45650</v>
       </c>
       <c r="J5" s="59">
-        <f t="shared" ref="J5:AW5" ca="1" si="0">I5+1</f>
+        <f t="shared" ref="J5:AW5" si="0">I5+1</f>
         <v>45651</v>
       </c>
       <c r="K5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45652</v>
       </c>
       <c r="L5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45653</v>
       </c>
       <c r="M5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45654</v>
       </c>
       <c r="N5" s="60">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45655</v>
       </c>
       <c r="O5" s="58">
-        <f ca="1">N5+1</f>
+        <f>N5+1</f>
         <v>45656</v>
       </c>
       <c r="P5" s="59">
-        <f ca="1">O5+1</f>
+        <f>O5+1</f>
         <v>45657</v>
       </c>
       <c r="Q5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45658</v>
       </c>
       <c r="R5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45659</v>
       </c>
       <c r="S5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45660</v>
       </c>
       <c r="T5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45661</v>
       </c>
       <c r="U5" s="60">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45662</v>
       </c>
       <c r="V5" s="58">
-        <f ca="1">U5+1</f>
+        <f>U5+1</f>
         <v>45663</v>
       </c>
       <c r="W5" s="59">
-        <f ca="1">V5+1</f>
+        <f>V5+1</f>
         <v>45664</v>
       </c>
       <c r="X5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45665</v>
       </c>
       <c r="Y5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45666</v>
       </c>
       <c r="Z5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45667</v>
       </c>
       <c r="AA5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45668</v>
       </c>
       <c r="AB5" s="60">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45669</v>
       </c>
       <c r="AC5" s="58">
-        <f ca="1">AB5+1</f>
+        <f>AB5+1</f>
         <v>45670</v>
       </c>
       <c r="AD5" s="59">
-        <f ca="1">AC5+1</f>
+        <f>AC5+1</f>
         <v>45671</v>
       </c>
       <c r="AE5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45672</v>
       </c>
       <c r="AF5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45673</v>
       </c>
       <c r="AG5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45674</v>
       </c>
       <c r="AH5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45675</v>
       </c>
       <c r="AI5" s="60">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45676</v>
       </c>
       <c r="AJ5" s="58">
-        <f ca="1">AI5+1</f>
+        <f>AI5+1</f>
         <v>45677</v>
       </c>
       <c r="AK5" s="59">
-        <f ca="1">AJ5+1</f>
+        <f>AJ5+1</f>
         <v>45678</v>
       </c>
       <c r="AL5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45679</v>
       </c>
       <c r="AM5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45680</v>
       </c>
       <c r="AN5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45681</v>
       </c>
       <c r="AO5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45682</v>
       </c>
       <c r="AP5" s="60">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45683</v>
       </c>
       <c r="AQ5" s="58">
-        <f ca="1">AP5+1</f>
+        <f>AP5+1</f>
         <v>45684</v>
       </c>
       <c r="AR5" s="59">
-        <f ca="1">AQ5+1</f>
+        <f>AQ5+1</f>
         <v>45685</v>
       </c>
       <c r="AS5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45686</v>
       </c>
       <c r="AT5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45687</v>
       </c>
       <c r="AU5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45688</v>
       </c>
       <c r="AV5" s="59">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45689</v>
       </c>
       <c r="AW5" s="60">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45690</v>
       </c>
       <c r="AX5" s="58">
-        <f ca="1">AW5+1</f>
+        <f>AW5+1</f>
         <v>45691</v>
       </c>
       <c r="AY5" s="59">
-        <f ca="1">AX5+1</f>
+        <f>AX5+1</f>
         <v>45692</v>
       </c>
       <c r="AZ5" s="59">
-        <f t="shared" ref="AZ5:BD5" ca="1" si="1">AY5+1</f>
+        <f t="shared" ref="AZ5:BD5" si="1">AY5+1</f>
         <v>45693</v>
       </c>
       <c r="BA5" s="59">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45694</v>
       </c>
       <c r="BB5" s="59">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45695</v>
       </c>
       <c r="BC5" s="59">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45696</v>
       </c>
       <c r="BD5" s="60">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45697</v>
       </c>
     </row>
     <row r="6" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="69" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -2128,199 +2116,199 @@
         <v>13</v>
       </c>
       <c r="H6" s="9" t="str">
-        <f t="shared" ref="H6:AM6" ca="1" si="2">LEFT(TEXT(H5,"ggg"),1)</f>
+        <f t="shared" ref="H6:AM6" si="2">LEFT(TEXT(H5,"ggg"),1)</f>
         <v>l</v>
       </c>
       <c r="I6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="J6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="K6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>g</v>
       </c>
       <c r="L6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>v</v>
       </c>
       <c r="M6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>s</v>
       </c>
       <c r="N6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>d</v>
       </c>
       <c r="O6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>l</v>
       </c>
       <c r="P6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="Q6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="R6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>g</v>
       </c>
       <c r="S6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>v</v>
       </c>
       <c r="T6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>s</v>
       </c>
       <c r="U6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>d</v>
       </c>
       <c r="V6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>l</v>
       </c>
       <c r="W6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="X6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="Y6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>g</v>
       </c>
       <c r="Z6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>v</v>
       </c>
       <c r="AA6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>s</v>
       </c>
       <c r="AB6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>d</v>
       </c>
       <c r="AC6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>l</v>
       </c>
       <c r="AD6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="AE6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="AF6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>g</v>
       </c>
       <c r="AG6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>v</v>
       </c>
       <c r="AH6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>s</v>
       </c>
       <c r="AI6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>d</v>
       </c>
       <c r="AJ6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>l</v>
       </c>
       <c r="AK6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="AL6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>m</v>
       </c>
       <c r="AM6" s="9" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>g</v>
       </c>
       <c r="AN6" s="9" t="str">
-        <f t="shared" ref="AN6:BD6" ca="1" si="3">LEFT(TEXT(AN5,"ggg"),1)</f>
+        <f t="shared" ref="AN6:BD6" si="3">LEFT(TEXT(AN5,"ggg"),1)</f>
         <v>v</v>
       </c>
       <c r="AO6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>s</v>
       </c>
       <c r="AP6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>d</v>
       </c>
       <c r="AQ6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>l</v>
       </c>
       <c r="AR6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>m</v>
       </c>
       <c r="AS6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>m</v>
       </c>
       <c r="AT6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>g</v>
       </c>
       <c r="AU6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>v</v>
       </c>
       <c r="AV6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>s</v>
       </c>
       <c r="AW6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>d</v>
       </c>
       <c r="AX6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>l</v>
       </c>
       <c r="AY6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>m</v>
       </c>
       <c r="AZ6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>m</v>
       </c>
       <c r="BA6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>g</v>
       </c>
       <c r="BB6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>v</v>
       </c>
       <c r="BC6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>s</v>
       </c>
       <c r="BD6" s="9" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>d</v>
       </c>
     </row>
@@ -2385,7 +2373,7 @@
       <c r="BD7" s="23"/>
     </row>
     <row r="8" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="72">
+      <c r="A8" s="70">
         <v>1</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -2399,24 +2387,24 @@
         <f t="shared" ref="G8" si="4">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
         <v/>
       </c>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="66"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="64"/>
       <c r="S8" s="23"/>
-      <c r="T8" s="66"/>
-      <c r="U8" s="66"/>
-      <c r="V8" s="66"/>
-      <c r="W8" s="66"/>
-      <c r="X8" s="66"/>
-      <c r="Y8" s="66"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
       <c r="Z8" s="23"/>
       <c r="AA8" s="23"/>
       <c r="AB8" s="23"/>
@@ -2461,35 +2449,35 @@
         <v>1</v>
       </c>
       <c r="E9" s="48">
-        <f ca="1">Inizio_progetto</f>
-        <v>45650</v>
+        <f>Inizio_progetto</f>
+        <v>45648</v>
       </c>
       <c r="F9" s="48">
-        <f ca="1">E9</f>
-        <v>45650</v>
+        <f>E9+1</f>
+        <v>45649</v>
       </c>
       <c r="G9" s="10">
-        <f t="shared" ref="G9:G26" ca="1" si="5">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
-        <v>1</v>
-      </c>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="64"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="64"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="63"/>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="66"/>
+        <f t="shared" ref="G9:G26" si="5">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="64"/>
       <c r="S9" s="23"/>
-      <c r="T9" s="66"/>
-      <c r="U9" s="66"/>
-      <c r="V9" s="66"/>
-      <c r="W9" s="66"/>
-      <c r="X9" s="66"/>
-      <c r="Y9" s="66"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="64"/>
       <c r="Z9" s="23"/>
       <c r="AA9" s="23"/>
       <c r="AB9" s="23"/>
@@ -2534,35 +2522,35 @@
         <v>0.9</v>
       </c>
       <c r="E10" s="48">
-        <f ca="1">F9</f>
-        <v>45650</v>
+        <f>F9</f>
+        <v>45649</v>
       </c>
       <c r="F10" s="48">
-        <f ca="1">E10</f>
-        <v>45650</v>
+        <f>E10</f>
+        <v>45649</v>
       </c>
       <c r="G10" s="10">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="63"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="23"/>
-      <c r="N10" s="64"/>
-      <c r="O10" s="64"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="66"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="64"/>
       <c r="S10" s="23"/>
-      <c r="T10" s="66"/>
-      <c r="U10" s="66"/>
-      <c r="V10" s="66"/>
-      <c r="W10" s="66"/>
-      <c r="X10" s="66"/>
-      <c r="Y10" s="66"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
       <c r="Z10" s="23"/>
       <c r="AA10" s="23"/>
       <c r="AB10" s="23"/>
@@ -2608,24 +2596,24 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="64"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="64"/>
-      <c r="O11" s="64"/>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="66"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="64"/>
       <c r="S11" s="23"/>
-      <c r="T11" s="66"/>
-      <c r="U11" s="66"/>
-      <c r="V11" s="66"/>
-      <c r="W11" s="66"/>
-      <c r="X11" s="66"/>
-      <c r="Y11" s="66"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
       <c r="Z11" s="23"/>
       <c r="AA11" s="23"/>
       <c r="AB11" s="23"/>
@@ -2670,35 +2658,35 @@
         <v>0.9</v>
       </c>
       <c r="E12" s="51">
-        <f ca="1">F10</f>
+        <f>F10+1</f>
         <v>45650</v>
       </c>
       <c r="F12" s="51">
-        <f ca="1">E12</f>
+        <f>E12</f>
         <v>45650</v>
       </c>
       <c r="G12" s="10">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="64"/>
-      <c r="P12" s="63"/>
-      <c r="Q12" s="63"/>
-      <c r="R12" s="66"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="64"/>
       <c r="S12" s="23"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="66"/>
-      <c r="V12" s="66"/>
-      <c r="W12" s="66"/>
-      <c r="X12" s="66"/>
-      <c r="Y12" s="66"/>
+      <c r="T12" s="64"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="64"/>
       <c r="Z12" s="23"/>
       <c r="AA12" s="23"/>
       <c r="AB12" s="23"/>
@@ -2737,41 +2725,41 @@
         <v>23</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D13" s="16">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="E13" s="51">
-        <f ca="1">E12+1</f>
-        <v>45651</v>
+        <f>E12</f>
+        <v>45650</v>
       </c>
       <c r="F13" s="51">
-        <f t="shared" ref="F13:F15" ca="1" si="6">E13</f>
-        <v>45651</v>
+        <f>E13+4</f>
+        <v>45654</v>
       </c>
       <c r="G13" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="64"/>
-      <c r="O13" s="64"/>
-      <c r="P13" s="63"/>
-      <c r="Q13" s="63"/>
-      <c r="R13" s="66"/>
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="64"/>
       <c r="S13" s="23"/>
-      <c r="T13" s="67"/>
-      <c r="U13" s="67"/>
-      <c r="V13" s="66"/>
-      <c r="W13" s="66"/>
-      <c r="X13" s="66"/>
-      <c r="Y13" s="66"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="64"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="64"/>
       <c r="Z13" s="23"/>
       <c r="AA13" s="23"/>
       <c r="AB13" s="23"/>
@@ -2810,41 +2798,41 @@
         <v>24</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D14" s="16">
         <v>0.4</v>
       </c>
       <c r="E14" s="51">
-        <f ca="1">E13</f>
-        <v>45651</v>
+        <f>E13</f>
+        <v>45650</v>
       </c>
       <c r="F14" s="51">
-        <f t="shared" ca="1" si="6"/>
-        <v>45651</v>
+        <f>E14+10</f>
+        <v>45660</v>
       </c>
       <c r="G14" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="64"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="64"/>
-      <c r="O14" s="64"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="63"/>
-      <c r="R14" s="66"/>
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="64"/>
       <c r="S14" s="23"/>
-      <c r="T14" s="67"/>
-      <c r="U14" s="67"/>
-      <c r="V14" s="66"/>
-      <c r="W14" s="66"/>
-      <c r="X14" s="66"/>
-      <c r="Y14" s="66"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="65"/>
+      <c r="V14" s="64"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="64"/>
+      <c r="Y14" s="64"/>
       <c r="Z14" s="23"/>
       <c r="AA14" s="23"/>
       <c r="AB14" s="23"/>
@@ -2883,41 +2871,41 @@
         <v>25</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D15" s="16">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E15" s="51">
-        <f t="shared" ref="E15" ca="1" si="7">E14</f>
-        <v>45651</v>
+        <f>E14</f>
+        <v>45650</v>
       </c>
       <c r="F15" s="51">
-        <f t="shared" ca="1" si="6"/>
-        <v>45651</v>
+        <f>E15+10</f>
+        <v>45660</v>
       </c>
       <c r="G15" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="64"/>
-      <c r="P15" s="63"/>
-      <c r="Q15" s="63"/>
-      <c r="R15" s="66"/>
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="64"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="67"/>
-      <c r="U15" s="67"/>
-      <c r="V15" s="66"/>
-      <c r="W15" s="66"/>
-      <c r="X15" s="66"/>
-      <c r="Y15" s="66"/>
+      <c r="T15" s="65"/>
+      <c r="U15" s="65"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
       <c r="Z15" s="23"/>
       <c r="AA15" s="23"/>
       <c r="AB15" s="23"/>
@@ -2956,41 +2944,41 @@
         <v>26</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D16" s="16">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E16" s="51">
-        <f ca="1">F15+2</f>
-        <v>45653</v>
+        <f>F13+1</f>
+        <v>45655</v>
       </c>
       <c r="F16" s="51">
-        <f ca="1">E16</f>
-        <v>45653</v>
+        <f>E16+5</f>
+        <v>45660</v>
       </c>
       <c r="G16" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="64"/>
-      <c r="O16" s="64"/>
-      <c r="P16" s="63"/>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="66"/>
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="64"/>
       <c r="S16" s="23"/>
-      <c r="T16" s="67"/>
-      <c r="U16" s="67"/>
-      <c r="V16" s="66"/>
-      <c r="W16" s="66"/>
-      <c r="X16" s="66"/>
-      <c r="Y16" s="66"/>
+      <c r="T16" s="65"/>
+      <c r="U16" s="65"/>
+      <c r="V16" s="64"/>
+      <c r="W16" s="64"/>
+      <c r="X16" s="64"/>
+      <c r="Y16" s="64"/>
       <c r="Z16" s="23"/>
       <c r="AA16" s="23"/>
       <c r="AB16" s="23"/>
@@ -3029,41 +3017,41 @@
         <v>27</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D17" s="16">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E17" s="51">
-        <f ca="1">E16</f>
-        <v>45653</v>
+        <f>E16</f>
+        <v>45655</v>
       </c>
       <c r="F17" s="51">
-        <f ca="1">E17</f>
-        <v>45653</v>
+        <f>E17+5</f>
+        <v>45660</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="63"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="64"/>
-      <c r="O17" s="64"/>
-      <c r="P17" s="63"/>
-      <c r="Q17" s="63"/>
-      <c r="R17" s="66"/>
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="64"/>
       <c r="S17" s="23"/>
-      <c r="T17" s="67"/>
-      <c r="U17" s="67"/>
-      <c r="V17" s="66"/>
-      <c r="W17" s="66"/>
-      <c r="X17" s="66"/>
-      <c r="Y17" s="66"/>
+      <c r="T17" s="65"/>
+      <c r="U17" s="65"/>
+      <c r="V17" s="64"/>
+      <c r="W17" s="64"/>
+      <c r="X17" s="64"/>
+      <c r="Y17" s="64"/>
       <c r="Z17" s="23"/>
       <c r="AA17" s="23"/>
       <c r="AB17" s="23"/>
@@ -3102,41 +3090,41 @@
         <v>28</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D18" s="16">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E18" s="51">
-        <f ca="1">E17</f>
-        <v>45653</v>
+        <f>E17</f>
+        <v>45655</v>
       </c>
       <c r="F18" s="51">
-        <f ca="1">E18</f>
-        <v>45653</v>
+        <f>E18+5</f>
+        <v>45660</v>
       </c>
       <c r="G18" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="64"/>
-      <c r="O18" s="64"/>
-      <c r="P18" s="63"/>
-      <c r="Q18" s="63"/>
-      <c r="R18" s="66"/>
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H18" s="71"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="64"/>
       <c r="S18" s="23"/>
-      <c r="T18" s="67"/>
-      <c r="U18" s="67"/>
-      <c r="V18" s="66"/>
-      <c r="W18" s="66"/>
-      <c r="X18" s="66"/>
-      <c r="Y18" s="66"/>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="64"/>
+      <c r="X18" s="64"/>
+      <c r="Y18" s="64"/>
       <c r="Z18" s="23"/>
       <c r="AA18" s="23"/>
       <c r="AB18" s="23"/>
@@ -3175,41 +3163,41 @@
         <v>17</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D19" s="16">
         <v>0</v>
       </c>
       <c r="E19" s="51">
-        <f ca="1">E13</f>
-        <v>45651</v>
+        <f>F18</f>
+        <v>45660</v>
       </c>
       <c r="F19" s="51">
-        <f ca="1">E19+2</f>
-        <v>45653</v>
+        <f>E19</f>
+        <v>45660</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>3</v>
-      </c>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="64"/>
-      <c r="O19" s="64"/>
-      <c r="P19" s="63"/>
-      <c r="Q19" s="63"/>
-      <c r="R19" s="66"/>
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="64"/>
       <c r="S19" s="23"/>
-      <c r="T19" s="66"/>
-      <c r="U19" s="66"/>
-      <c r="V19" s="66"/>
-      <c r="W19" s="66"/>
-      <c r="X19" s="66"/>
-      <c r="Y19" s="66"/>
+      <c r="T19" s="64"/>
+      <c r="U19" s="64"/>
+      <c r="V19" s="64"/>
+      <c r="W19" s="64"/>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="64"/>
       <c r="Z19" s="23"/>
       <c r="AA19" s="23"/>
       <c r="AB19" s="23"/>
@@ -3254,35 +3242,35 @@
         <v>0</v>
       </c>
       <c r="E20" s="51">
-        <f ca="1">F19+1</f>
-        <v>45654</v>
+        <f>E19</f>
+        <v>45660</v>
       </c>
       <c r="F20" s="51">
-        <f ca="1">E20+1</f>
-        <v>45655</v>
+        <f>E20</f>
+        <v>45660</v>
       </c>
       <c r="G20" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="64"/>
-      <c r="P20" s="63"/>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="66"/>
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="71"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="64"/>
       <c r="S20" s="23"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="66"/>
-      <c r="V20" s="66"/>
-      <c r="W20" s="66"/>
-      <c r="X20" s="66"/>
-      <c r="Y20" s="66"/>
+      <c r="T20" s="64"/>
+      <c r="U20" s="64"/>
+      <c r="V20" s="64"/>
+      <c r="W20" s="64"/>
+      <c r="X20" s="64"/>
+      <c r="Y20" s="64"/>
       <c r="Z20" s="23"/>
       <c r="AA20" s="23"/>
       <c r="AB20" s="23"/>
@@ -3316,7 +3304,7 @@
       <c r="BD20" s="23"/>
     </row>
     <row r="21" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="68"/>
+      <c r="A21" s="66"/>
       <c r="B21" s="17" t="s">
         <v>18</v>
       </c>
@@ -3328,24 +3316,24 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="63"/>
-      <c r="Q21" s="63"/>
-      <c r="R21" s="66"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="64"/>
       <c r="S21" s="23"/>
-      <c r="T21" s="66"/>
-      <c r="U21" s="66"/>
-      <c r="V21" s="66"/>
-      <c r="W21" s="66"/>
-      <c r="X21" s="66"/>
-      <c r="Y21" s="66"/>
+      <c r="T21" s="64"/>
+      <c r="U21" s="64"/>
+      <c r="V21" s="64"/>
+      <c r="W21" s="64"/>
+      <c r="X21" s="64"/>
+      <c r="Y21" s="64"/>
       <c r="Z21" s="23"/>
       <c r="AA21" s="23"/>
       <c r="AB21" s="23"/>
@@ -3379,7 +3367,7 @@
       <c r="BD21" s="23"/>
     </row>
     <row r="22" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="69"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="41" t="s">
         <v>44</v>
       </c>
@@ -3390,35 +3378,34 @@
         <v>0</v>
       </c>
       <c r="E22" s="54">
-        <f ca="1">F20+1</f>
-        <v>45656</v>
+        <v>45661</v>
       </c>
       <c r="F22" s="54">
-        <f ca="1">E22+7</f>
-        <v>45663</v>
+        <f>E22+5</f>
+        <v>45666</v>
       </c>
       <c r="G22" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>8</v>
-      </c>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="66"/>
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="71"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="64"/>
       <c r="S22" s="23"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
+      <c r="T22" s="64"/>
+      <c r="U22" s="64"/>
+      <c r="V22" s="64"/>
+      <c r="W22" s="64"/>
+      <c r="X22" s="64"/>
+      <c r="Y22" s="64"/>
       <c r="Z22" s="23"/>
       <c r="AA22" s="23"/>
       <c r="AB22" s="23"/>
@@ -3452,7 +3439,7 @@
       <c r="BD22" s="23"/>
     </row>
     <row r="23" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="69"/>
+      <c r="A23" s="67"/>
       <c r="B23" s="41" t="s">
         <v>19</v>
       </c>
@@ -3463,35 +3450,35 @@
         <v>0</v>
       </c>
       <c r="E23" s="54">
-        <f ca="1">E22</f>
-        <v>45656</v>
+        <f>E22</f>
+        <v>45661</v>
       </c>
       <c r="F23" s="54">
-        <f ca="1">E23+7</f>
-        <v>45663</v>
+        <f>E23+5</f>
+        <v>45666</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>8</v>
-      </c>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="66"/>
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="64"/>
       <c r="S23" s="23"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66"/>
-      <c r="V23" s="66"/>
-      <c r="W23" s="66"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
+      <c r="T23" s="64"/>
+      <c r="U23" s="64"/>
+      <c r="V23" s="64"/>
+      <c r="W23" s="64"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
       <c r="Z23" s="23"/>
       <c r="AA23" s="23"/>
       <c r="AB23" s="23"/>
@@ -3525,7 +3512,7 @@
       <c r="BD23" s="23"/>
     </row>
     <row r="24" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="69"/>
+      <c r="A24" s="67"/>
       <c r="B24" s="41" t="s">
         <v>41</v>
       </c>
@@ -3536,35 +3523,35 @@
         <v>0</v>
       </c>
       <c r="E24" s="54">
-        <f ca="1">E23</f>
-        <v>45656</v>
+        <f>E23</f>
+        <v>45661</v>
       </c>
       <c r="F24" s="54">
-        <f ca="1">E24+3</f>
-        <v>45659</v>
+        <f>E24+3</f>
+        <v>45664</v>
       </c>
       <c r="G24" s="10">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="63"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="64"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="66"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="64"/>
       <c r="S24" s="23"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="66"/>
-      <c r="V24" s="66"/>
-      <c r="W24" s="66"/>
-      <c r="X24" s="66"/>
-      <c r="Y24" s="66"/>
+      <c r="T24" s="64"/>
+      <c r="U24" s="64"/>
+      <c r="V24" s="64"/>
+      <c r="W24" s="64"/>
+      <c r="X24" s="64"/>
+      <c r="Y24" s="64"/>
       <c r="Z24" s="23"/>
       <c r="AA24" s="23"/>
       <c r="AB24" s="23"/>
@@ -3598,7 +3585,7 @@
       <c r="BD24" s="23"/>
     </row>
     <row r="25" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="69"/>
+      <c r="A25" s="67"/>
       <c r="B25" s="41" t="s">
         <v>30</v>
       </c>
@@ -3609,35 +3596,35 @@
         <v>0</v>
       </c>
       <c r="E25" s="54">
-        <f ca="1">F22+1</f>
-        <v>45664</v>
+        <f>F22+1</f>
+        <v>45667</v>
       </c>
       <c r="F25" s="54">
-        <f ca="1">E25+4</f>
-        <v>45668</v>
+        <f>E25+4</f>
+        <v>45671</v>
       </c>
       <c r="G25" s="10">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="63"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="64"/>
-      <c r="O25" s="64"/>
-      <c r="P25" s="63"/>
-      <c r="Q25" s="63"/>
-      <c r="R25" s="66"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="64"/>
       <c r="S25" s="23"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="66"/>
-      <c r="V25" s="66"/>
-      <c r="W25" s="66"/>
-      <c r="X25" s="66"/>
-      <c r="Y25" s="66"/>
+      <c r="T25" s="64"/>
+      <c r="U25" s="64"/>
+      <c r="V25" s="64"/>
+      <c r="W25" s="64"/>
+      <c r="X25" s="64"/>
+      <c r="Y25" s="64"/>
       <c r="Z25" s="23"/>
       <c r="AA25" s="23"/>
       <c r="AB25" s="23"/>
@@ -3671,7 +3658,7 @@
       <c r="BD25" s="23"/>
     </row>
     <row r="26" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="70"/>
+      <c r="A26" s="68"/>
       <c r="B26" s="61" t="s">
         <v>20</v>
       </c>
@@ -3682,35 +3669,35 @@
         <v>0</v>
       </c>
       <c r="E26" s="54">
-        <f ca="1">F25-1</f>
-        <v>45667</v>
-      </c>
-      <c r="F26" s="73">
-        <f ca="1">E26+2</f>
-        <v>45669</v>
+        <f>F25-1</f>
+        <v>45670</v>
+      </c>
+      <c r="F26" s="54">
+        <f>E26+2</f>
+        <v>45672</v>
       </c>
       <c r="G26" s="10">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="64"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="64"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="66"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="71"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="64"/>
       <c r="S26" s="23"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="66"/>
-      <c r="V26" s="66"/>
-      <c r="W26" s="66"/>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="66"/>
+      <c r="T26" s="64"/>
+      <c r="U26" s="64"/>
+      <c r="V26" s="64"/>
+      <c r="W26" s="64"/>
+      <c r="X26" s="64"/>
+      <c r="Y26" s="64"/>
       <c r="Z26" s="23"/>
       <c r="AA26" s="23"/>
       <c r="AB26" s="23"/>
@@ -3753,27 +3740,27 @@
       <c r="E27" s="55"/>
       <c r="F27" s="56"/>
       <c r="G27" s="10" t="str">
-        <f t="shared" ref="G27:G34" si="8">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <f t="shared" ref="G27:G34" si="6">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
         <v/>
       </c>
-      <c r="H27" s="64"/>
-      <c r="I27" s="64"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="64"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="64"/>
-      <c r="P27" s="63"/>
-      <c r="Q27" s="63"/>
-      <c r="R27" s="66"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="64"/>
       <c r="S27" s="23"/>
-      <c r="T27" s="66"/>
-      <c r="U27" s="66"/>
-      <c r="V27" s="66"/>
-      <c r="W27" s="66"/>
-      <c r="X27" s="66"/>
-      <c r="Y27" s="66"/>
+      <c r="T27" s="64"/>
+      <c r="U27" s="64"/>
+      <c r="V27" s="64"/>
+      <c r="W27" s="64"/>
+      <c r="X27" s="64"/>
+      <c r="Y27" s="64"/>
       <c r="Z27" s="23"/>
       <c r="AA27" s="23"/>
       <c r="AB27" s="23"/>
@@ -3818,35 +3805,35 @@
         <v>0</v>
       </c>
       <c r="E28" s="57">
-        <f ca="1">F25+1</f>
-        <v>45669</v>
+        <f>F25+1</f>
+        <v>45672</v>
       </c>
       <c r="F28" s="57">
-        <f ca="1">E28+3</f>
-        <v>45672</v>
+        <f>E28+3</f>
+        <v>45675</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="H28" s="64"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="64"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
-      <c r="R28" s="66"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="71"/>
+      <c r="J28" s="71"/>
+      <c r="K28" s="71"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="64"/>
       <c r="S28" s="23"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="66"/>
-      <c r="V28" s="66"/>
-      <c r="W28" s="66"/>
-      <c r="X28" s="66"/>
-      <c r="Y28" s="66"/>
+      <c r="T28" s="64"/>
+      <c r="U28" s="64"/>
+      <c r="V28" s="64"/>
+      <c r="W28" s="64"/>
+      <c r="X28" s="64"/>
+      <c r="Y28" s="64"/>
       <c r="Z28" s="23"/>
       <c r="AA28" s="23"/>
       <c r="AB28" s="23"/>
@@ -3880,7 +3867,7 @@
       <c r="BD28" s="23"/>
     </row>
     <row r="29" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="68">
+      <c r="A29" s="66">
         <v>2</v>
       </c>
       <c r="B29" s="17" t="s">
@@ -3891,27 +3878,27 @@
       <c r="E29" s="52"/>
       <c r="F29" s="53"/>
       <c r="G29" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="H29" s="64"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="23"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="64"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="63"/>
-      <c r="Q29" s="63"/>
-      <c r="R29" s="66"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="64"/>
       <c r="S29" s="23"/>
-      <c r="T29" s="66"/>
-      <c r="U29" s="66"/>
-      <c r="V29" s="66"/>
-      <c r="W29" s="66"/>
-      <c r="X29" s="66"/>
-      <c r="Y29" s="66"/>
+      <c r="T29" s="64"/>
+      <c r="U29" s="64"/>
+      <c r="V29" s="64"/>
+      <c r="W29" s="64"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="64"/>
       <c r="Z29" s="23"/>
       <c r="AA29" s="23"/>
       <c r="AB29" s="23"/>
@@ -3956,35 +3943,35 @@
         <v>0</v>
       </c>
       <c r="E30" s="54">
-        <f ca="1">F28</f>
-        <v>45672</v>
+        <f>F28</f>
+        <v>45675</v>
       </c>
       <c r="F30" s="54">
-        <f ca="1">E30+5</f>
-        <v>45677</v>
+        <f>E30+5</f>
+        <v>45680</v>
       </c>
       <c r="G30" s="10">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="63"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="63"/>
-      <c r="Q30" s="63"/>
-      <c r="R30" s="66"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="71"/>
+      <c r="N30" s="71"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="64"/>
       <c r="S30" s="23"/>
-      <c r="T30" s="66"/>
-      <c r="U30" s="66"/>
-      <c r="V30" s="66"/>
-      <c r="W30" s="66"/>
-      <c r="X30" s="66"/>
-      <c r="Y30" s="66"/>
+      <c r="T30" s="64"/>
+      <c r="U30" s="64"/>
+      <c r="V30" s="64"/>
+      <c r="W30" s="64"/>
+      <c r="X30" s="64"/>
+      <c r="Y30" s="64"/>
       <c r="Z30" s="23"/>
       <c r="AA30" s="23"/>
       <c r="AB30" s="23"/>
@@ -4029,35 +4016,35 @@
         <v>0</v>
       </c>
       <c r="E31" s="54">
-        <f ca="1">E30</f>
-        <v>45672</v>
+        <f>E30</f>
+        <v>45675</v>
       </c>
       <c r="F31" s="54">
-        <f ca="1">E31+5</f>
-        <v>45677</v>
+        <f>E31+5</f>
+        <v>45680</v>
       </c>
       <c r="G31" s="10">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="H31" s="64"/>
-      <c r="I31" s="64"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="63"/>
-      <c r="R31" s="66"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="71"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="64"/>
       <c r="S31" s="23"/>
-      <c r="T31" s="66"/>
-      <c r="U31" s="66"/>
-      <c r="V31" s="66"/>
-      <c r="W31" s="66"/>
-      <c r="X31" s="66"/>
-      <c r="Y31" s="66"/>
+      <c r="T31" s="64"/>
+      <c r="U31" s="64"/>
+      <c r="V31" s="64"/>
+      <c r="W31" s="64"/>
+      <c r="X31" s="64"/>
+      <c r="Y31" s="64"/>
       <c r="Z31" s="23"/>
       <c r="AA31" s="23"/>
       <c r="AB31" s="23"/>
@@ -4102,35 +4089,35 @@
         <v>0</v>
       </c>
       <c r="E32" s="54">
-        <f ca="1">E31</f>
-        <v>45672</v>
+        <f>E31</f>
+        <v>45675</v>
       </c>
       <c r="F32" s="54">
-        <f ca="1">E32+3</f>
-        <v>45675</v>
+        <f>E32+3</f>
+        <v>45678</v>
       </c>
       <c r="G32" s="10">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="63"/>
-      <c r="K32" s="64"/>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="64"/>
-      <c r="O32" s="64"/>
-      <c r="P32" s="63"/>
-      <c r="Q32" s="63"/>
-      <c r="R32" s="66"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="64"/>
       <c r="S32" s="23"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="66"/>
-      <c r="V32" s="66"/>
-      <c r="W32" s="66"/>
-      <c r="X32" s="66"/>
-      <c r="Y32" s="66"/>
+      <c r="T32" s="64"/>
+      <c r="U32" s="64"/>
+      <c r="V32" s="64"/>
+      <c r="W32" s="64"/>
+      <c r="X32" s="64"/>
+      <c r="Y32" s="64"/>
       <c r="Z32" s="23"/>
       <c r="AA32" s="23"/>
       <c r="AB32" s="23"/>
@@ -4175,35 +4162,35 @@
         <v>0</v>
       </c>
       <c r="E33" s="54">
-        <f ca="1">F30+1</f>
-        <v>45678</v>
+        <f>F30+1</f>
+        <v>45681</v>
       </c>
       <c r="F33" s="54">
-        <f ca="1">E33+2</f>
-        <v>45680</v>
+        <f>E33+2</f>
+        <v>45683</v>
       </c>
       <c r="G33" s="10">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="63"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="23"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="64"/>
-      <c r="O33" s="64"/>
-      <c r="P33" s="63"/>
-      <c r="Q33" s="63"/>
-      <c r="R33" s="66"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="71"/>
+      <c r="N33" s="71"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="64"/>
       <c r="S33" s="23"/>
-      <c r="T33" s="66"/>
-      <c r="U33" s="66"/>
-      <c r="V33" s="66"/>
-      <c r="W33" s="66"/>
-      <c r="X33" s="66"/>
-      <c r="Y33" s="66"/>
+      <c r="T33" s="64"/>
+      <c r="U33" s="64"/>
+      <c r="V33" s="64"/>
+      <c r="W33" s="64"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="64"/>
       <c r="Z33" s="23"/>
       <c r="AA33" s="23"/>
       <c r="AB33" s="23"/>
@@ -4248,35 +4235,35 @@
         <v>0</v>
       </c>
       <c r="E34" s="54">
-        <f ca="1">F33-1</f>
-        <v>45679</v>
+        <f>F33-1</f>
+        <v>45682</v>
       </c>
       <c r="F34" s="54">
-        <f ca="1">E34+1</f>
-        <v>45680</v>
+        <f>E34+1</f>
+        <v>45683</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="63"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="64"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="66"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="71"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="64"/>
       <c r="S34" s="23"/>
-      <c r="T34" s="66"/>
-      <c r="U34" s="66"/>
-      <c r="V34" s="66"/>
-      <c r="W34" s="66"/>
-      <c r="X34" s="66"/>
-      <c r="Y34" s="66"/>
+      <c r="T34" s="64"/>
+      <c r="U34" s="64"/>
+      <c r="V34" s="64"/>
+      <c r="W34" s="64"/>
+      <c r="X34" s="64"/>
+      <c r="Y34" s="64"/>
       <c r="Z34" s="23"/>
       <c r="AA34" s="23"/>
       <c r="AB34" s="23"/>
@@ -4319,24 +4306,24 @@
       <c r="E35" s="55"/>
       <c r="F35" s="56"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="63"/>
-      <c r="K35" s="64"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="64"/>
-      <c r="P35" s="63"/>
-      <c r="Q35" s="63"/>
-      <c r="R35" s="66"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="71"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="71"/>
+      <c r="N35" s="71"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="64"/>
       <c r="S35" s="23"/>
-      <c r="T35" s="66"/>
-      <c r="U35" s="66"/>
-      <c r="V35" s="66"/>
-      <c r="W35" s="66"/>
-      <c r="X35" s="66"/>
-      <c r="Y35" s="66"/>
+      <c r="T35" s="64"/>
+      <c r="U35" s="64"/>
+      <c r="V35" s="64"/>
+      <c r="W35" s="64"/>
+      <c r="X35" s="64"/>
+      <c r="Y35" s="64"/>
       <c r="Z35" s="23"/>
       <c r="AA35" s="23"/>
       <c r="AB35" s="23"/>
@@ -4381,35 +4368,35 @@
         <v>0</v>
       </c>
       <c r="E36" s="57">
-        <f ca="1">F34+1</f>
-        <v>45681</v>
+        <f>F34+1</f>
+        <v>45684</v>
       </c>
       <c r="F36" s="57">
-        <f ca="1">E36+3</f>
-        <v>45684</v>
+        <f>E36+3</f>
+        <v>45687</v>
       </c>
       <c r="G36" s="10">
-        <f ca="1">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
         <v>4</v>
       </c>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="63"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="64"/>
-      <c r="O36" s="64"/>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="63"/>
-      <c r="R36" s="66"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="71"/>
+      <c r="N36" s="71"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="64"/>
       <c r="S36" s="23"/>
-      <c r="T36" s="66"/>
-      <c r="U36" s="66"/>
-      <c r="V36" s="66"/>
-      <c r="W36" s="66"/>
-      <c r="X36" s="66"/>
-      <c r="Y36" s="66"/>
+      <c r="T36" s="64"/>
+      <c r="U36" s="64"/>
+      <c r="V36" s="64"/>
+      <c r="W36" s="64"/>
+      <c r="X36" s="64"/>
+      <c r="Y36" s="64"/>
       <c r="Z36" s="23"/>
       <c r="AA36" s="23"/>
       <c r="AB36" s="23"/>
@@ -4454,35 +4441,35 @@
         <v>0</v>
       </c>
       <c r="E37" s="57">
-        <f ca="1">F36</f>
-        <v>45684</v>
+        <f>F36</f>
+        <v>45687</v>
       </c>
       <c r="F37" s="57">
-        <f ca="1">F36</f>
-        <v>45684</v>
+        <f>F36</f>
+        <v>45687</v>
       </c>
       <c r="G37" s="10">
-        <f ca="1">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
         <v>1</v>
       </c>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="63"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="64"/>
-      <c r="O37" s="64"/>
-      <c r="P37" s="63"/>
-      <c r="Q37" s="63"/>
-      <c r="R37" s="66"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="71"/>
+      <c r="O37" s="71"/>
+      <c r="P37" s="71"/>
+      <c r="Q37" s="71"/>
+      <c r="R37" s="64"/>
       <c r="S37" s="23"/>
-      <c r="T37" s="66"/>
-      <c r="U37" s="66"/>
-      <c r="V37" s="66"/>
-      <c r="W37" s="66"/>
-      <c r="X37" s="66"/>
-      <c r="Y37" s="66"/>
+      <c r="T37" s="64"/>
+      <c r="U37" s="64"/>
+      <c r="V37" s="64"/>
+      <c r="W37" s="64"/>
+      <c r="X37" s="64"/>
+      <c r="Y37" s="64"/>
       <c r="Z37" s="23"/>
       <c r="AA37" s="23"/>
       <c r="AB37" s="23"/>
@@ -4614,7 +4601,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="65"/>
+      <c r="A2" s="63"/>
       <c r="B2" t="s">
         <v>39</v>
       </c>

--- a/Diagramma di Gantt.xlsx
+++ b/Diagramma di Gantt.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B98E4B0-6ECD-4569-A369-5CAE2C233606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A947D93-FB68-46C1-B930-C26BDEAFC42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PianificazioneProgetto" sheetId="11" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
   <si>
     <t>Come creare la pianificazione di un progetto in questo foglio di lavoro.
 Immettere il titolo del progetto nella cella B1. 
@@ -174,9 +174,6 @@
   </si>
   <si>
     <t>Implementazione del database</t>
-  </si>
-  <si>
-    <t>Teruzzi, Messa</t>
   </si>
   <si>
     <t>Tentori, Ronchi</t>
@@ -226,7 +223,7 @@
     <numFmt numFmtId="168" formatCode="d\ mmm\ yyyy"/>
     <numFmt numFmtId="169" formatCode="d"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -417,6 +414,13 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -959,7 +963,7 @@
     <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1176,6 +1180,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1771,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
@@ -1785,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H2" s="45"/>
     </row>
@@ -2095,7 +2102,7 @@
     </row>
     <row r="6" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>6</v>
@@ -2443,7 +2450,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="13">
         <v>1</v>
@@ -2725,7 +2732,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="16">
         <v>0.9</v>
@@ -2798,7 +2805,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="16">
         <v>0.4</v>
@@ -2871,7 +2878,7 @@
         <v>25</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="16">
         <v>0.4</v>
@@ -2944,10 +2951,10 @@
         <v>26</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E16" s="51">
         <f>F13+1</f>
@@ -3017,10 +3024,10 @@
         <v>27</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E17" s="51">
         <f>E16</f>
@@ -3090,7 +3097,7 @@
         <v>28</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="16">
         <v>0.8</v>
@@ -3163,7 +3170,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="16">
         <v>0</v>
@@ -3236,10 +3243,10 @@
         <v>40</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D20" s="16">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E20" s="51">
         <f>E19</f>
@@ -3309,7 +3316,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="35"/>
-      <c r="D21" s="18"/>
+      <c r="D21" s="78"/>
       <c r="E21" s="52"/>
       <c r="F21" s="53"/>
       <c r="G21" s="10" t="str">
@@ -3369,10 +3376,10 @@
     <row r="22" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="67"/>
       <c r="B22" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="36" t="s">
         <v>44</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>45</v>
       </c>
       <c r="D22" s="19">
         <v>0</v>
@@ -3733,7 +3740,7 @@
     <row r="27" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="20"/>
       <c r="B27" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="21"/>
@@ -3796,7 +3803,7 @@
     <row r="28" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="42"/>
       <c r="B28" s="42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" s="38" t="s">
         <v>33</v>
@@ -3934,10 +3941,10 @@
     <row r="30" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="41"/>
       <c r="B30" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="36" t="s">
         <v>44</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>45</v>
       </c>
       <c r="D30" s="19">
         <v>0</v>
@@ -4299,7 +4306,7 @@
     <row r="35" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="20"/>
       <c r="B35" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="21"/>
@@ -4359,7 +4366,7 @@
     <row r="36" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="42"/>
       <c r="B36" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" s="38" t="s">
         <v>33</v>
@@ -4612,23 +4619,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003574973502B84C42B74035BA8AADE1A3" ma:contentTypeVersion="9" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ba771f4a91505810405fb99ac35d176">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8f4f0557-6568-4af7-94c6-f11cb446b9b2" xmlns:ns4="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3481e8909782aae8d117dfcc8e1ba87" ns3:_="" ns4:_="">
     <xsd:import namespace="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
@@ -4823,32 +4813,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A7A2A5-3EAC-4111-8CE5-4F4CD491981F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4865,4 +4847,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Diagramma di Gantt.xlsx
+++ b/Diagramma di Gantt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A947D93-FB68-46C1-B930-C26BDEAFC42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C963F21E-0EFB-4A86-B687-3E514412D4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
   <si>
     <t>Come creare la pianificazione di un progetto in questo foglio di lavoro.
 Immettere il titolo del progetto nella cella B1. 
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>Tentori, Ronchi, Messa, Teruzzi</t>
+  </si>
+  <si>
+    <t>Ricerca SpringBoot</t>
+  </si>
+  <si>
+    <t>Ricerca React</t>
   </si>
 </sst>
 </file>
@@ -1164,6 +1170,9 @@
     <xf numFmtId="0" fontId="12" fillId="46" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="27" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
@@ -1180,9 +1189,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1759,7 +1765,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BD37"/>
+  <dimension ref="A1:BD39"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" style="25" customWidth="1"/>
@@ -1803,96 +1809,96 @@
       <c r="B3" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="73"/>
-      <c r="E3" s="77">
+      <c r="D3" s="74"/>
+      <c r="E3" s="78">
         <v>45648</v>
       </c>
-      <c r="F3" s="77"/>
+      <c r="F3" s="78"/>
     </row>
     <row r="4" spans="1:56" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="73"/>
+      <c r="D4" s="74"/>
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="H4" s="74">
+      <c r="H4" s="75">
         <f>H5</f>
         <v>45649</v>
       </c>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="74">
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="75">
         <f>O5</f>
         <v>45656</v>
       </c>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="74">
+      <c r="P4" s="76"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="76"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="77"/>
+      <c r="V4" s="75">
         <f>V5</f>
         <v>45663</v>
       </c>
-      <c r="W4" s="75"/>
-      <c r="X4" s="75"/>
-      <c r="Y4" s="75"/>
-      <c r="Z4" s="75"/>
-      <c r="AA4" s="75"/>
-      <c r="AB4" s="76"/>
-      <c r="AC4" s="74">
+      <c r="W4" s="76"/>
+      <c r="X4" s="76"/>
+      <c r="Y4" s="76"/>
+      <c r="Z4" s="76"/>
+      <c r="AA4" s="76"/>
+      <c r="AB4" s="77"/>
+      <c r="AC4" s="75">
         <f>AC5</f>
         <v>45670</v>
       </c>
-      <c r="AD4" s="75"/>
-      <c r="AE4" s="75"/>
-      <c r="AF4" s="75"/>
-      <c r="AG4" s="75"/>
-      <c r="AH4" s="75"/>
-      <c r="AI4" s="76"/>
-      <c r="AJ4" s="74">
+      <c r="AD4" s="76"/>
+      <c r="AE4" s="76"/>
+      <c r="AF4" s="76"/>
+      <c r="AG4" s="76"/>
+      <c r="AH4" s="76"/>
+      <c r="AI4" s="77"/>
+      <c r="AJ4" s="75">
         <f>AJ5</f>
         <v>45677</v>
       </c>
-      <c r="AK4" s="75"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="75"/>
-      <c r="AN4" s="75"/>
-      <c r="AO4" s="75"/>
-      <c r="AP4" s="76"/>
-      <c r="AQ4" s="74">
+      <c r="AK4" s="76"/>
+      <c r="AL4" s="76"/>
+      <c r="AM4" s="76"/>
+      <c r="AN4" s="76"/>
+      <c r="AO4" s="76"/>
+      <c r="AP4" s="77"/>
+      <c r="AQ4" s="75">
         <f>AQ5</f>
         <v>45684</v>
       </c>
-      <c r="AR4" s="75"/>
-      <c r="AS4" s="75"/>
-      <c r="AT4" s="75"/>
-      <c r="AU4" s="75"/>
-      <c r="AV4" s="75"/>
-      <c r="AW4" s="76"/>
-      <c r="AX4" s="74">
+      <c r="AR4" s="76"/>
+      <c r="AS4" s="76"/>
+      <c r="AT4" s="76"/>
+      <c r="AU4" s="76"/>
+      <c r="AV4" s="76"/>
+      <c r="AW4" s="77"/>
+      <c r="AX4" s="75">
         <f>AX5</f>
         <v>45691</v>
       </c>
-      <c r="AY4" s="75"/>
-      <c r="AZ4" s="75"/>
-      <c r="BA4" s="75"/>
-      <c r="BB4" s="75"/>
-      <c r="BC4" s="75"/>
-      <c r="BD4" s="76"/>
+      <c r="AY4" s="76"/>
+      <c r="AZ4" s="76"/>
+      <c r="BA4" s="76"/>
+      <c r="BB4" s="76"/>
+      <c r="BC4" s="76"/>
+      <c r="BD4" s="77"/>
     </row>
     <row r="5" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
@@ -2464,7 +2470,7 @@
         <v>45649</v>
       </c>
       <c r="G9" s="10">
-        <f t="shared" ref="G9:G26" si="5">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <f t="shared" ref="G9:G28" si="5">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
         <v>2</v>
       </c>
       <c r="H9" s="71"/>
@@ -3173,7 +3179,7 @@
         <v>52</v>
       </c>
       <c r="D19" s="16">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="51">
         <f>F18</f>
@@ -3240,26 +3246,23 @@
     <row r="20" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="40"/>
       <c r="B20" s="40" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="16">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="E20" s="51">
-        <f>E19</f>
+        <f t="shared" ref="E20:E21" si="6">F19</f>
         <v>45660</v>
       </c>
       <c r="F20" s="51">
-        <f>E20</f>
-        <v>45660</v>
-      </c>
-      <c r="G20" s="10">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
+        <f>E20+1</f>
+        <v>45661</v>
+      </c>
+      <c r="G20" s="10"/>
       <c r="H20" s="71"/>
       <c r="I20" s="71"/>
       <c r="J20" s="71"/>
@@ -3311,18 +3314,25 @@
       <c r="BD20" s="23"/>
     </row>
     <row r="21" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="66"/>
-      <c r="B21" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="A21" s="40"/>
+      <c r="B21" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="E21" s="51">
+        <f>E20</f>
+        <v>45660</v>
+      </c>
+      <c r="F21" s="51">
+        <f>E21+1</f>
+        <v>45661</v>
+      </c>
+      <c r="G21" s="10"/>
       <c r="H21" s="71"/>
       <c r="I21" s="71"/>
       <c r="J21" s="71"/>
@@ -3374,26 +3384,27 @@
       <c r="BD21" s="23"/>
     </row>
     <row r="22" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="67"/>
-      <c r="B22" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="19">
-        <v>0</v>
-      </c>
-      <c r="E22" s="54">
-        <v>45661</v>
-      </c>
-      <c r="F22" s="54">
-        <f>E22+5</f>
-        <v>45666</v>
+      <c r="A22" s="40"/>
+      <c r="B22" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="E22" s="51">
+        <f>E19</f>
+        <v>45660</v>
+      </c>
+      <c r="F22" s="51">
+        <f>E22</f>
+        <v>45660</v>
       </c>
       <c r="G22" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -3446,27 +3457,17 @@
       <c r="BD22" s="23"/>
     </row>
     <row r="23" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="67"/>
-      <c r="B23" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="19">
-        <v>0</v>
-      </c>
-      <c r="E23" s="54">
-        <f>E22</f>
-        <v>45661</v>
-      </c>
-      <c r="F23" s="54">
-        <f>E23+5</f>
-        <v>45666</v>
-      </c>
-      <c r="G23" s="10">
+      <c r="A23" s="66"/>
+      <c r="B23" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="35"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v/>
       </c>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -3521,25 +3522,24 @@
     <row r="24" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="67"/>
       <c r="B24" s="41" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D24" s="19">
         <v>0</v>
       </c>
       <c r="E24" s="54">
-        <f>E23</f>
         <v>45661</v>
       </c>
       <c r="F24" s="54">
-        <f>E24+3</f>
-        <v>45664</v>
+        <f>E24+5</f>
+        <v>45666</v>
       </c>
       <c r="G24" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H24" s="71"/>
       <c r="I24" s="71"/>
@@ -3594,25 +3594,25 @@
     <row r="25" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="67"/>
       <c r="B25" s="41" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D25" s="19">
         <v>0</v>
       </c>
       <c r="E25" s="54">
-        <f>F22+1</f>
-        <v>45667</v>
+        <f>E24</f>
+        <v>45661</v>
       </c>
       <c r="F25" s="54">
-        <f>E25+4</f>
-        <v>45671</v>
+        <f>E25+5</f>
+        <v>45666</v>
       </c>
       <c r="G25" s="10">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="71"/>
       <c r="I25" s="71"/>
@@ -3665,27 +3665,27 @@
       <c r="BD25" s="23"/>
     </row>
     <row r="26" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="68"/>
-      <c r="B26" s="61" t="s">
-        <v>20</v>
+      <c r="A26" s="67"/>
+      <c r="B26" s="41" t="s">
+        <v>41</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D26" s="19">
         <v>0</v>
       </c>
       <c r="E26" s="54">
-        <f>F25-1</f>
-        <v>45670</v>
+        <f>E25</f>
+        <v>45661</v>
       </c>
       <c r="F26" s="54">
-        <f>E26+2</f>
-        <v>45672</v>
+        <f>E26+3</f>
+        <v>45664</v>
       </c>
       <c r="G26" s="10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="71"/>
       <c r="I26" s="71"/>
@@ -3738,17 +3738,27 @@
       <c r="BD26" s="23"/>
     </row>
     <row r="27" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="10" t="str">
-        <f t="shared" ref="G27:G34" si="6">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
-        <v/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="19">
+        <v>0</v>
+      </c>
+      <c r="E27" s="54">
+        <f>F24+1</f>
+        <v>45667</v>
+      </c>
+      <c r="F27" s="54">
+        <f>E27+4</f>
+        <v>45671</v>
+      </c>
+      <c r="G27" s="10">
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
@@ -3801,27 +3811,27 @@
       <c r="BD27" s="23"/>
     </row>
     <row r="28" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42"/>
-      <c r="B28" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="22">
+      <c r="A28" s="68"/>
+      <c r="B28" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="19">
         <v>0</v>
       </c>
-      <c r="E28" s="57">
-        <f>F25+1</f>
+      <c r="E28" s="54">
+        <f>F27-1</f>
+        <v>45670</v>
+      </c>
+      <c r="F28" s="54">
+        <f>E28+2</f>
         <v>45672</v>
       </c>
-      <c r="F28" s="57">
-        <f>E28+3</f>
-        <v>45675</v>
-      </c>
       <c r="G28" s="10">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="H28" s="71"/>
       <c r="I28" s="71"/>
@@ -3874,18 +3884,16 @@
       <c r="BD28" s="23"/>
     </row>
     <row r="29" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="66">
-        <v>2</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="53"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="37"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="56"/>
       <c r="G29" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G29:G36" si="7">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
         <v/>
       </c>
       <c r="H29" s="71"/>
@@ -3939,27 +3947,27 @@
       <c r="BD29" s="23"/>
     </row>
     <row r="30" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="41"/>
-      <c r="B30" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="19">
+      <c r="A30" s="42"/>
+      <c r="B30" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="22">
         <v>0</v>
       </c>
-      <c r="E30" s="54">
-        <f>F28</f>
+      <c r="E30" s="57">
+        <f>F27+1</f>
+        <v>45672</v>
+      </c>
+      <c r="F30" s="57">
+        <f>E30+3</f>
         <v>45675</v>
       </c>
-      <c r="F30" s="54">
-        <f>E30+5</f>
-        <v>45680</v>
-      </c>
       <c r="G30" s="10">
-        <f t="shared" si="6"/>
-        <v>6</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H30" s="71"/>
       <c r="I30" s="71"/>
@@ -4011,28 +4019,20 @@
       <c r="BC30" s="23"/>
       <c r="BD30" s="23"/>
     </row>
-    <row r="31" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="41"/>
-      <c r="B31" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="19">
-        <v>0</v>
-      </c>
-      <c r="E31" s="54">
-        <f>E30</f>
-        <v>45675</v>
-      </c>
-      <c r="F31" s="54">
-        <f>E31+5</f>
-        <v>45680</v>
-      </c>
-      <c r="G31" s="10">
-        <f t="shared" si="6"/>
-        <v>6</v>
+    <row r="31" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="66">
+        <v>2</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="35"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="10" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4084,28 +4084,28 @@
       <c r="BC31" s="23"/>
       <c r="BD31" s="23"/>
     </row>
-    <row r="32" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="41"/>
       <c r="B32" s="41" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D32" s="19">
         <v>0</v>
       </c>
       <c r="E32" s="54">
-        <f>E31</f>
+        <f>F30</f>
         <v>45675</v>
       </c>
       <c r="F32" s="54">
-        <f>E32+3</f>
-        <v>45678</v>
+        <f>E32+5</f>
+        <v>45680</v>
       </c>
       <c r="G32" s="10">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="H32" s="71"/>
       <c r="I32" s="71"/>
@@ -4160,25 +4160,25 @@
     <row r="33" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="41"/>
       <c r="B33" s="41" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D33" s="19">
         <v>0</v>
       </c>
       <c r="E33" s="54">
-        <f>F30+1</f>
-        <v>45681</v>
+        <f>E32</f>
+        <v>45675</v>
       </c>
       <c r="F33" s="54">
-        <f>E33+2</f>
-        <v>45683</v>
+        <f>E33+5</f>
+        <v>45680</v>
       </c>
       <c r="G33" s="10">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="H33" s="71"/>
       <c r="I33" s="71"/>
@@ -4231,27 +4231,27 @@
       <c r="BD33" s="23"/>
     </row>
     <row r="34" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="61"/>
-      <c r="B34" s="61" t="s">
-        <v>20</v>
+      <c r="A34" s="41"/>
+      <c r="B34" s="41" t="s">
+        <v>41</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D34" s="19">
         <v>0</v>
       </c>
       <c r="E34" s="54">
-        <f>F33-1</f>
-        <v>45682</v>
+        <f>E33</f>
+        <v>45675</v>
       </c>
       <c r="F34" s="54">
-        <f>E34+1</f>
-        <v>45683</v>
+        <f>E34+3</f>
+        <v>45678</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="H34" s="71"/>
       <c r="I34" s="71"/>
@@ -4304,15 +4304,28 @@
       <c r="BD34" s="23"/>
     </row>
     <row r="35" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="20"/>
-      <c r="B35" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="55"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="10"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="19">
+        <v>0</v>
+      </c>
+      <c r="E35" s="54">
+        <f>F32+1</f>
+        <v>45681</v>
+      </c>
+      <c r="F35" s="54">
+        <f>E35+2</f>
+        <v>45683</v>
+      </c>
+      <c r="G35" s="10">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
       <c r="J35" s="71"/>
@@ -4363,28 +4376,28 @@
       <c r="BC35" s="23"/>
       <c r="BD35" s="23"/>
     </row>
-    <row r="36" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="42"/>
-      <c r="B36" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="22">
+    <row r="36" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="61"/>
+      <c r="B36" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="19">
         <v>0</v>
       </c>
-      <c r="E36" s="57">
-        <f>F34+1</f>
-        <v>45684</v>
-      </c>
-      <c r="F36" s="57">
-        <f>E36+3</f>
-        <v>45687</v>
+      <c r="E36" s="54">
+        <f>F35-1</f>
+        <v>45682</v>
+      </c>
+      <c r="F36" s="54">
+        <f>E36+1</f>
+        <v>45683</v>
       </c>
       <c r="G36" s="10">
-        <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="H36" s="71"/>
       <c r="I36" s="71"/>
@@ -4437,28 +4450,15 @@
       <c r="BD36" s="23"/>
     </row>
     <row r="37" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="42"/>
-      <c r="B37" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="22">
-        <v>0</v>
-      </c>
-      <c r="E37" s="57">
-        <f>F36</f>
-        <v>45687</v>
-      </c>
-      <c r="F37" s="57">
-        <f>F36</f>
-        <v>45687</v>
-      </c>
-      <c r="G37" s="10">
-        <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
-        <v>1</v>
-      </c>
+      <c r="A37" s="20"/>
+      <c r="B37" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="37"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="10"/>
       <c r="H37" s="71"/>
       <c r="I37" s="71"/>
       <c r="J37" s="71"/>
@@ -4509,6 +4509,152 @@
       <c r="BC37" s="23"/>
       <c r="BD37" s="23"/>
     </row>
+    <row r="38" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="42"/>
+      <c r="B38" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="22">
+        <v>0</v>
+      </c>
+      <c r="E38" s="57">
+        <f>F36+1</f>
+        <v>45684</v>
+      </c>
+      <c r="F38" s="57">
+        <f>E38+3</f>
+        <v>45687</v>
+      </c>
+      <c r="G38" s="10">
+        <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <v>4</v>
+      </c>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="64"/>
+      <c r="S38" s="23"/>
+      <c r="T38" s="64"/>
+      <c r="U38" s="64"/>
+      <c r="V38" s="64"/>
+      <c r="W38" s="64"/>
+      <c r="X38" s="64"/>
+      <c r="Y38" s="64"/>
+      <c r="Z38" s="23"/>
+      <c r="AA38" s="23"/>
+      <c r="AB38" s="23"/>
+      <c r="AC38" s="23"/>
+      <c r="AD38" s="23"/>
+      <c r="AE38" s="23"/>
+      <c r="AF38" s="23"/>
+      <c r="AG38" s="23"/>
+      <c r="AH38" s="23"/>
+      <c r="AI38" s="23"/>
+      <c r="AJ38" s="23"/>
+      <c r="AK38" s="23"/>
+      <c r="AL38" s="23"/>
+      <c r="AM38" s="23"/>
+      <c r="AN38" s="23"/>
+      <c r="AO38" s="23"/>
+      <c r="AP38" s="23"/>
+      <c r="AQ38" s="23"/>
+      <c r="AR38" s="23"/>
+      <c r="AS38" s="23"/>
+      <c r="AT38" s="23"/>
+      <c r="AU38" s="23"/>
+      <c r="AV38" s="23"/>
+      <c r="AW38" s="23"/>
+      <c r="AX38" s="23"/>
+      <c r="AY38" s="23"/>
+      <c r="AZ38" s="23"/>
+      <c r="BA38" s="23"/>
+      <c r="BB38" s="23"/>
+      <c r="BC38" s="23"/>
+      <c r="BD38" s="23"/>
+    </row>
+    <row r="39" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="42"/>
+      <c r="B39" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="22">
+        <v>0</v>
+      </c>
+      <c r="E39" s="57">
+        <f>F38</f>
+        <v>45687</v>
+      </c>
+      <c r="F39" s="57">
+        <f>F38</f>
+        <v>45687</v>
+      </c>
+      <c r="G39" s="10">
+        <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <v>1</v>
+      </c>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="64"/>
+      <c r="S39" s="23"/>
+      <c r="T39" s="64"/>
+      <c r="U39" s="64"/>
+      <c r="V39" s="64"/>
+      <c r="W39" s="64"/>
+      <c r="X39" s="64"/>
+      <c r="Y39" s="64"/>
+      <c r="Z39" s="23"/>
+      <c r="AA39" s="23"/>
+      <c r="AB39" s="23"/>
+      <c r="AC39" s="23"/>
+      <c r="AD39" s="23"/>
+      <c r="AE39" s="23"/>
+      <c r="AF39" s="23"/>
+      <c r="AG39" s="23"/>
+      <c r="AH39" s="23"/>
+      <c r="AI39" s="23"/>
+      <c r="AJ39" s="23"/>
+      <c r="AK39" s="23"/>
+      <c r="AL39" s="23"/>
+      <c r="AM39" s="23"/>
+      <c r="AN39" s="23"/>
+      <c r="AO39" s="23"/>
+      <c r="AP39" s="23"/>
+      <c r="AQ39" s="23"/>
+      <c r="AR39" s="23"/>
+      <c r="AS39" s="23"/>
+      <c r="AT39" s="23"/>
+      <c r="AU39" s="23"/>
+      <c r="AV39" s="23"/>
+      <c r="AW39" s="23"/>
+      <c r="AX39" s="23"/>
+      <c r="AY39" s="23"/>
+      <c r="AZ39" s="23"/>
+      <c r="BA39" s="23"/>
+      <c r="BB39" s="23"/>
+      <c r="BC39" s="23"/>
+      <c r="BD39" s="23"/>
+    </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C3:D3"/>
@@ -4522,7 +4668,7 @@
     <mergeCell ref="V4:AB4"/>
     <mergeCell ref="AC4:AI4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D7:D37">
+  <conditionalFormatting sqref="D7:D39">
     <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4536,27 +4682,27 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:BC37">
+  <conditionalFormatting sqref="H5:BC39">
     <cfRule type="expression" dxfId="4" priority="3">
       <formula>AND(TODAY()&gt;=H$5,TODAY()&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:BC37">
+  <conditionalFormatting sqref="H7:BC39">
     <cfRule type="expression" dxfId="3" priority="2" stopIfTrue="1">
       <formula>AND(fine_attività&gt;=H$5,inizio_attività&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:BD37">
+  <conditionalFormatting sqref="H7:BD39">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(inizio_attività&lt;=H$5,ROUNDDOWN((fine_attività-inizio_attività+1)*avanzamento_attività,0)+inizio_attività-1&gt;=H$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BD5:BD37">
+  <conditionalFormatting sqref="BD5:BD39">
     <cfRule type="expression" dxfId="1" priority="38">
       <formula>AND(TODAY()&gt;=BD$5,TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BD7:BD37">
+  <conditionalFormatting sqref="BD7:BD39">
     <cfRule type="expression" dxfId="0" priority="42" stopIfTrue="1">
       <formula>AND(fine_attività&gt;=BD$5,inizio_attività&lt;#REF!)</formula>
     </cfRule>
@@ -4588,7 +4734,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D37</xm:sqref>
+          <xm:sqref>D7:D39</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4619,6 +4765,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003574973502B84C42B74035BA8AADE1A3" ma:contentTypeVersion="9" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ba771f4a91505810405fb99ac35d176">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8f4f0557-6568-4af7-94c6-f11cb446b9b2" xmlns:ns4="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3481e8909782aae8d117dfcc8e1ba87" ns3:_="" ns4:_="">
     <xsd:import namespace="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
@@ -4813,24 +4976,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A7A2A5-3EAC-4111-8CE5-4F4CD491981F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4847,29 +5018,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Diagramma di Gantt.xlsx
+++ b/Diagramma di Gantt.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C963F21E-0EFB-4A86-B687-3E514412D4A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A312E701-743B-415A-83C6-AC4B690795F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
   <si>
     <t>Come creare la pianificazione di un progetto in questo foglio di lavoro.
 Immettere il titolo del progetto nella cella B1. 
@@ -149,12 +149,6 @@
     <t>Tentori</t>
   </si>
   <si>
-    <t>Ronchi, Messa</t>
-  </si>
-  <si>
-    <t>Tentori, Teruzzi</t>
-  </si>
-  <si>
     <t>Messa</t>
   </si>
   <si>
@@ -182,9 +176,6 @@
     <t xml:space="preserve">Sviluppo del backend </t>
   </si>
   <si>
-    <t>Messa, Ronchi</t>
-  </si>
-  <si>
     <t>ITERAZIONE</t>
   </si>
   <si>
@@ -213,6 +204,36 @@
   </si>
   <si>
     <t>Ricerca React</t>
+  </si>
+  <si>
+    <t>Teruzzi, Messa</t>
+  </si>
+  <si>
+    <t>Tentori, Ronchi, Messa</t>
+  </si>
+  <si>
+    <t>Ronchi, Messa, Tentori</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Revisione diagrammi</t>
+  </si>
+  <si>
+    <t>Teruzzi, Messa, Ronchi</t>
+  </si>
+  <si>
+    <t>Revisione del database</t>
+  </si>
+  <si>
+    <t>Ronchi, Tentori</t>
+  </si>
+  <si>
+    <t>Ronchi, Messa, Tentori, Teruzzi</t>
+  </si>
+  <si>
+    <t>Tentori, Teruzzi, Ronchi, Messa</t>
   </si>
 </sst>
 </file>
@@ -969,7 +990,7 @@
     <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1189,6 +1210,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1765,7 +1789,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BD39"/>
+  <dimension ref="A1:BD40"/>
   <sheetFormatPr defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" style="25" customWidth="1"/>
@@ -1784,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
@@ -1798,7 +1822,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H2" s="45"/>
     </row>
@@ -1807,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" s="73" t="s">
         <v>7</v>
@@ -2108,7 +2132,7 @@
     </row>
     <row r="6" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="69" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>6</v>
@@ -2456,7 +2480,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D9" s="13">
         <v>1</v>
@@ -2529,10 +2553,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" s="13">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E10" s="48">
         <f>F9</f>
@@ -2665,10 +2689,10 @@
         <v>22</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D12" s="16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E12" s="51">
         <f>F10+1</f>
@@ -2738,10 +2762,10 @@
         <v>23</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" s="16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E13" s="51">
         <f>E12</f>
@@ -2811,10 +2835,10 @@
         <v>24</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" s="16">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="51">
         <f>E13</f>
@@ -2884,10 +2908,10 @@
         <v>25</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D15" s="16">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="51">
         <f>E14</f>
@@ -2957,10 +2981,10 @@
         <v>26</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D16" s="16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E16" s="51">
         <f>F13+1</f>
@@ -3030,10 +3054,10 @@
         <v>27</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D17" s="16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E17" s="51">
         <f>E16</f>
@@ -3103,10 +3127,10 @@
         <v>28</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D18" s="16">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E18" s="51">
         <f>E17</f>
@@ -3176,10 +3200,10 @@
         <v>17</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D19" s="16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E19" s="51">
         <f>F18</f>
@@ -3246,16 +3270,16 @@
     <row r="20" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="40"/>
       <c r="B20" s="40" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C20" s="34" t="s">
         <v>31</v>
       </c>
       <c r="D20" s="16">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="51">
-        <f t="shared" ref="E20:E21" si="6">F19</f>
+        <f t="shared" ref="E20" si="6">F19</f>
         <v>45660</v>
       </c>
       <c r="F20" s="51">
@@ -3316,13 +3340,13 @@
     <row r="21" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="40"/>
       <c r="B21" s="40" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="16">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="51">
         <f>E20</f>
@@ -3386,25 +3410,25 @@
     <row r="22" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40"/>
       <c r="B22" s="40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C22" s="34" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E22" s="51">
         <f>E19</f>
         <v>45660</v>
       </c>
       <c r="F22" s="51">
-        <f>E22</f>
-        <v>45660</v>
+        <f>E22+1</f>
+        <v>45661</v>
       </c>
       <c r="G22" s="10">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="71"/>
       <c r="I22" s="71"/>
@@ -3522,24 +3546,24 @@
     <row r="24" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="67"/>
       <c r="B24" s="41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D24" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="54">
         <v>45661</v>
       </c>
       <c r="F24" s="54">
-        <f>E24+5</f>
-        <v>45666</v>
+        <f>E24+17</f>
+        <v>45678</v>
       </c>
       <c r="G24" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H24" s="71"/>
       <c r="I24" s="71"/>
@@ -3597,22 +3621,22 @@
         <v>19</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D25" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="54">
         <f>E24</f>
         <v>45661</v>
       </c>
       <c r="F25" s="54">
-        <f>E25+5</f>
-        <v>45666</v>
+        <f>E25+17</f>
+        <v>45678</v>
       </c>
       <c r="G25" s="10">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H25" s="71"/>
       <c r="I25" s="71"/>
@@ -3667,25 +3691,25 @@
     <row r="26" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="67"/>
       <c r="B26" s="41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C26" s="36" t="s">
         <v>32</v>
       </c>
       <c r="D26" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="54">
         <f>E25</f>
         <v>45661</v>
       </c>
       <c r="F26" s="54">
-        <f>E26+3</f>
-        <v>45664</v>
+        <f>E26+6</f>
+        <v>45667</v>
       </c>
       <c r="G26" s="10">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H26" s="71"/>
       <c r="I26" s="71"/>
@@ -3743,18 +3767,18 @@
         <v>30</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D27" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="54">
-        <f>F24+1</f>
-        <v>45667</v>
+        <f>E24+17</f>
+        <v>45678</v>
       </c>
       <c r="F27" s="54">
         <f>E27+4</f>
-        <v>45671</v>
+        <v>45682</v>
       </c>
       <c r="G27" s="10">
         <f t="shared" si="5"/>
@@ -3816,22 +3840,22 @@
         <v>20</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D28" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="54">
-        <f>F27-1</f>
-        <v>45670</v>
+        <f>E27+1</f>
+        <v>45679</v>
       </c>
       <c r="F28" s="54">
-        <f>E28+2</f>
-        <v>45672</v>
+        <f>E28</f>
+        <v>45679</v>
       </c>
       <c r="G28" s="10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="71"/>
       <c r="I28" s="71"/>
@@ -3886,14 +3910,14 @@
     <row r="29" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20"/>
       <c r="B29" s="20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="21"/>
       <c r="E29" s="55"/>
       <c r="F29" s="56"/>
       <c r="G29" s="10" t="str">
-        <f t="shared" ref="G29:G36" si="7">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <f t="shared" ref="G29:G37" si="7">IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
         <v/>
       </c>
       <c r="H29" s="71"/>
@@ -3949,21 +3973,21 @@
     <row r="30" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="42"/>
       <c r="B30" s="42" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D30" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="57">
-        <f>F27+1</f>
-        <v>45672</v>
+        <f>F28</f>
+        <v>45679</v>
       </c>
       <c r="F30" s="57">
         <f>E30+3</f>
-        <v>45675</v>
+        <v>45682</v>
       </c>
       <c r="G30" s="10">
         <f t="shared" si="7"/>
@@ -4020,19 +4044,18 @@
       <c r="BD30" s="23"/>
     </row>
     <row r="31" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="66">
+      <c r="A31" s="79">
         <v>2</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+      <c r="B31" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="33"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="H31" s="71"/>
       <c r="I31" s="71"/>
@@ -4085,27 +4108,26 @@
       <c r="BD31" s="23"/>
     </row>
     <row r="32" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="41"/>
-      <c r="B32" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="19">
-        <v>0</v>
-      </c>
-      <c r="E32" s="54">
+      <c r="A32" s="40"/>
+      <c r="B32" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="16">
+        <v>1</v>
+      </c>
+      <c r="E32" s="51">
         <f>F30</f>
-        <v>45675</v>
-      </c>
-      <c r="F32" s="54">
-        <f>E32+5</f>
-        <v>45680</v>
+        <v>45682</v>
+      </c>
+      <c r="F32" s="51">
+        <f>E32+4</f>
+        <v>45686</v>
       </c>
       <c r="G32" s="10">
-        <f t="shared" si="7"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H32" s="71"/>
       <c r="I32" s="71"/>
@@ -4157,28 +4179,18 @@
       <c r="BC32" s="23"/>
       <c r="BD32" s="23"/>
     </row>
-    <row r="33" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="41"/>
-      <c r="B33" s="41" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="19">
-        <v>0</v>
-      </c>
-      <c r="E33" s="54">
-        <f>E32</f>
-        <v>45675</v>
-      </c>
-      <c r="F33" s="54">
-        <f>E33+5</f>
-        <v>45680</v>
-      </c>
-      <c r="G33" s="10">
+    <row r="33" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="66"/>
+      <c r="B33" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="35"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="10" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v/>
       </c>
       <c r="H33" s="71"/>
       <c r="I33" s="71"/>
@@ -4230,28 +4242,28 @@
       <c r="BC33" s="23"/>
       <c r="BD33" s="23"/>
     </row>
-    <row r="34" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="41"/>
       <c r="B34" s="41" t="s">
         <v>41</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D34" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="54">
-        <f>E33</f>
-        <v>45675</v>
+        <f>F30</f>
+        <v>45682</v>
       </c>
       <c r="F34" s="54">
-        <f>E34+3</f>
-        <v>45678</v>
+        <f>E34+2</f>
+        <v>45684</v>
       </c>
       <c r="G34" s="10">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H34" s="71"/>
       <c r="I34" s="71"/>
@@ -4306,21 +4318,21 @@
     <row r="35" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="41"/>
       <c r="B35" s="41" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="54">
-        <f>F32+1</f>
-        <v>45681</v>
+        <f>E34</f>
+        <v>45682</v>
       </c>
       <c r="F35" s="54">
         <f>E35+2</f>
-        <v>45683</v>
+        <v>45684</v>
       </c>
       <c r="G35" s="10">
         <f t="shared" si="7"/>
@@ -4377,27 +4389,27 @@
       <c r="BD35" s="23"/>
     </row>
     <row r="36" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="61"/>
-      <c r="B36" s="61" t="s">
-        <v>20</v>
+      <c r="A36" s="41"/>
+      <c r="B36" s="41" t="s">
+        <v>58</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D36" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="54">
-        <f>F35-1</f>
+        <f>E35</f>
         <v>45682</v>
       </c>
       <c r="F36" s="54">
-        <f>E36+1</f>
-        <v>45683</v>
+        <f>E36</f>
+        <v>45682</v>
       </c>
       <c r="G36" s="10">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="71"/>
       <c r="I36" s="71"/>
@@ -4450,15 +4462,28 @@
       <c r="BD36" s="23"/>
     </row>
     <row r="37" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="20"/>
-      <c r="B37" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="37"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="10"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="19">
+        <v>1</v>
+      </c>
+      <c r="E37" s="54">
+        <f>F34</f>
+        <v>45684</v>
+      </c>
+      <c r="F37" s="54">
+        <f>E37+1</f>
+        <v>45685</v>
+      </c>
+      <c r="G37" s="10">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
       <c r="H37" s="71"/>
       <c r="I37" s="71"/>
       <c r="J37" s="71"/>
@@ -4509,29 +4534,16 @@
       <c r="BC37" s="23"/>
       <c r="BD37" s="23"/>
     </row>
-    <row r="38" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="42"/>
-      <c r="B38" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="22">
-        <v>0</v>
-      </c>
-      <c r="E38" s="57">
-        <f>F36+1</f>
-        <v>45684</v>
-      </c>
-      <c r="F38" s="57">
-        <f>E38+3</f>
-        <v>45687</v>
-      </c>
-      <c r="G38" s="10">
-        <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
-        <v>4</v>
-      </c>
+    <row r="38" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="20"/>
+      <c r="B38" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="10"/>
       <c r="H38" s="71"/>
       <c r="I38" s="71"/>
       <c r="J38" s="71"/>
@@ -4582,28 +4594,28 @@
       <c r="BC38" s="23"/>
       <c r="BD38" s="23"/>
     </row>
-    <row r="39" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:56" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="42"/>
       <c r="B39" s="42" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D39" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="57">
-        <f>F38</f>
-        <v>45687</v>
+        <f>F35</f>
+        <v>45684</v>
       </c>
       <c r="F39" s="57">
-        <f>F38</f>
-        <v>45687</v>
+        <f>E39+2</f>
+        <v>45686</v>
       </c>
       <c r="G39" s="10">
         <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" s="71"/>
       <c r="I39" s="71"/>
@@ -4655,6 +4667,79 @@
       <c r="BC39" s="23"/>
       <c r="BD39" s="23"/>
     </row>
+    <row r="40" spans="1:56" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="42"/>
+      <c r="B40" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="22">
+        <v>1</v>
+      </c>
+      <c r="E40" s="57">
+        <f>E39</f>
+        <v>45684</v>
+      </c>
+      <c r="F40" s="57">
+        <f>F39</f>
+        <v>45686</v>
+      </c>
+      <c r="G40" s="10">
+        <f>IF(OR(ISBLANK(inizio_attività),ISBLANK(fine_attività)),"",fine_attività-inizio_attività+1)</f>
+        <v>3</v>
+      </c>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="71"/>
+      <c r="Q40" s="71"/>
+      <c r="R40" s="64"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="64"/>
+      <c r="U40" s="64"/>
+      <c r="V40" s="64"/>
+      <c r="W40" s="64"/>
+      <c r="X40" s="64"/>
+      <c r="Y40" s="64"/>
+      <c r="Z40" s="23"/>
+      <c r="AA40" s="23"/>
+      <c r="AB40" s="23"/>
+      <c r="AC40" s="23"/>
+      <c r="AD40" s="23"/>
+      <c r="AE40" s="23"/>
+      <c r="AF40" s="23"/>
+      <c r="AG40" s="23"/>
+      <c r="AH40" s="23"/>
+      <c r="AI40" s="23"/>
+      <c r="AJ40" s="23"/>
+      <c r="AK40" s="23"/>
+      <c r="AL40" s="23"/>
+      <c r="AM40" s="23"/>
+      <c r="AN40" s="23"/>
+      <c r="AO40" s="23"/>
+      <c r="AP40" s="23"/>
+      <c r="AQ40" s="23"/>
+      <c r="AR40" s="23"/>
+      <c r="AS40" s="23"/>
+      <c r="AT40" s="23"/>
+      <c r="AU40" s="23"/>
+      <c r="AV40" s="23"/>
+      <c r="AW40" s="23"/>
+      <c r="AX40" s="23"/>
+      <c r="AY40" s="23"/>
+      <c r="AZ40" s="23"/>
+      <c r="BA40" s="23"/>
+      <c r="BB40" s="23"/>
+      <c r="BC40" s="23"/>
+      <c r="BD40" s="23"/>
+    </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C3:D3"/>
@@ -4668,7 +4753,7 @@
     <mergeCell ref="V4:AB4"/>
     <mergeCell ref="AC4:AI4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D7:D39">
+  <conditionalFormatting sqref="D7:D40">
     <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -4682,32 +4767,32 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:BC39">
+  <conditionalFormatting sqref="H5:BC40">
     <cfRule type="expression" dxfId="4" priority="3">
       <formula>AND(TODAY()&gt;=H$5,TODAY()&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:BC39">
+  <conditionalFormatting sqref="H7:BC40">
     <cfRule type="expression" dxfId="3" priority="2" stopIfTrue="1">
       <formula>AND(fine_attività&gt;=H$5,inizio_attività&lt;I$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:BD39">
+  <conditionalFormatting sqref="H7:BD40">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>AND(inizio_attività&lt;=H$5,ROUNDDOWN((fine_attività-inizio_attività+1)*avanzamento_attività,0)+inizio_attività-1&gt;=H$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BD5:BD39">
+  <conditionalFormatting sqref="BD5:BD40">
     <cfRule type="expression" dxfId="1" priority="38">
       <formula>AND(TODAY()&gt;=BD$5,TODAY()&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BD7:BD39">
+  <conditionalFormatting sqref="BD7:BD40">
     <cfRule type="expression" dxfId="0" priority="42" stopIfTrue="1">
       <formula>AND(fine_attività&gt;=BD$5,inizio_attività&lt;#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Visualizza settimana:" prompt="Cambiando questo numero si scorre la visualizzazione del diagramma di Gantt." sqref="E4" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
     </dataValidation>
@@ -4734,7 +4819,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D39</xm:sqref>
+          <xm:sqref>D7:D40</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -4750,13 +4835,13 @@
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="62"/>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="63"/>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -4765,23 +4850,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003574973502B84C42B74035BA8AADE1A3" ma:contentTypeVersion="9" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="1ba771f4a91505810405fb99ac35d176">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8f4f0557-6568-4af7-94c6-f11cb446b9b2" xmlns:ns4="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3481e8909782aae8d117dfcc8e1ba87" ns3:_="" ns4:_="">
     <xsd:import namespace="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
@@ -4976,32 +5044,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26A7A2A5-3EAC-4111-8CE5-4F4CD491981F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5018,4 +5078,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8f4f0557-6568-4af7-94c6-f11cb446b9b2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="5a27f7c0-5079-4b07-ba64-6dc03dd2d3af"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>